--- a/통합 견적서 자동 생성 에이전트 템플릿 파일.xlsx
+++ b/통합 견적서 자동 생성 에이전트 템플릿 파일.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\user\Desktop\견적서작성\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DE36C2C7-19A5-48B1-A914-A2877E8DC7F8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D1FE2539-9B22-44F7-AB0E-D5A11BE4A1D5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="25080" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="32400" yWindow="3975" windowWidth="21600" windowHeight="11385" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="본견적서" sheetId="1" r:id="rId1"/>
@@ -1034,7 +1034,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="178">
+  <cellXfs count="177">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
@@ -1335,60 +1335,24 @@
     <xf numFmtId="0" fontId="3" fillId="2" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="47" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="45" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="47" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="35" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="45" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="28" fillId="2" borderId="48" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="47" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="51" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="51" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="49" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="44" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="10" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
+    <xf numFmtId="3" fontId="1" fillId="0" borderId="51" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="18" fillId="2" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="178" fontId="21" fillId="3" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="3" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="51" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="36" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="40" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="41" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="25" fillId="3" borderId="40" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="42" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="176" fontId="9" fillId="2" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
@@ -1396,6 +1360,7 @@
     <xf numFmtId="177" fontId="22" fillId="3" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="4" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1425,43 +1390,82 @@
     <xf numFmtId="0" fontId="10" fillId="2" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="51" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="51" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="51" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="40" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="41" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="25" fillId="3" borderId="40" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="42" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="45" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="45" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="28" fillId="2" borderId="48" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="49" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="44" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="10" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="2" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="178" fontId="21" fillId="3" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="3" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="27" fillId="2" borderId="44" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="46" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="47" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="34" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="34" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="178" fontId="3" fillId="2" borderId="23" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="3" fontId="3" fillId="2" borderId="23" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="36" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="5" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="47" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="47" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -1484,29 +1488,24 @@
     <xf numFmtId="178" fontId="15" fillId="5" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="47" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="35" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="34" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="47" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="34" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="178" fontId="3" fillId="2" borderId="23" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="51" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="51" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+    <xf numFmtId="3" fontId="3" fillId="2" borderId="23" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="51" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="51" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="51" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="27" fillId="2" borderId="44" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="51" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="3" fontId="1" fillId="0" borderId="51" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="47" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="46" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -2139,18 +2138,18 @@
     <row r="7" spans="1:26" ht="67.5" customHeight="1">
       <c r="A7" s="1"/>
       <c r="B7" s="1"/>
-      <c r="C7" s="133"/>
-      <c r="D7" s="111"/>
+      <c r="C7" s="114"/>
+      <c r="D7" s="113"/>
       <c r="E7" s="10" t="s">
         <v>1</v>
       </c>
       <c r="F7" s="10"/>
-      <c r="G7" s="134"/>
-      <c r="H7" s="111"/>
-      <c r="I7" s="135" t="s">
+      <c r="G7" s="115"/>
+      <c r="H7" s="113"/>
+      <c r="I7" s="116" t="s">
         <v>2</v>
       </c>
-      <c r="J7" s="111"/>
+      <c r="J7" s="113"/>
       <c r="K7" s="7"/>
       <c r="L7" s="1"/>
       <c r="M7" s="1"/>
@@ -2202,15 +2201,15 @@
       <c r="C9" s="14" t="s">
         <v>3</v>
       </c>
-      <c r="D9" s="136"/>
-      <c r="E9" s="137"/>
-      <c r="F9" s="137"/>
+      <c r="D9" s="117"/>
+      <c r="E9" s="118"/>
+      <c r="F9" s="118"/>
       <c r="G9" s="14" t="s">
         <v>6</v>
       </c>
-      <c r="H9" s="138"/>
-      <c r="I9" s="137"/>
-      <c r="J9" s="137"/>
+      <c r="H9" s="119"/>
+      <c r="I9" s="118"/>
+      <c r="J9" s="118"/>
       <c r="K9" s="7"/>
       <c r="L9" s="1"/>
       <c r="M9" s="2"/>
@@ -2298,10 +2297,10 @@
       <c r="C12" s="28" t="s">
         <v>7</v>
       </c>
-      <c r="D12" s="142" t="s">
+      <c r="D12" s="123" t="s">
         <v>0</v>
       </c>
-      <c r="E12" s="131"/>
+      <c r="E12" s="111"/>
       <c r="F12" s="30"/>
       <c r="G12" s="26" t="s">
         <v>9</v>
@@ -2309,10 +2308,10 @@
       <c r="H12" s="26" t="s">
         <v>26</v>
       </c>
-      <c r="I12" s="139" t="s">
+      <c r="I12" s="120" t="s">
         <v>27</v>
       </c>
-      <c r="J12" s="141" t="s">
+      <c r="J12" s="122" t="s">
         <v>28</v>
       </c>
       <c r="K12" s="7"/>
@@ -2336,8 +2335,8 @@
       <c r="A13" s="1"/>
       <c r="B13" s="12"/>
       <c r="C13" s="28"/>
-      <c r="D13" s="143"/>
-      <c r="E13" s="131"/>
+      <c r="D13" s="124"/>
+      <c r="E13" s="111"/>
       <c r="F13" s="35"/>
       <c r="G13" s="26" t="s">
         <v>17</v>
@@ -2345,8 +2344,8 @@
       <c r="H13" s="26" t="s">
         <v>18</v>
       </c>
-      <c r="I13" s="140"/>
-      <c r="J13" s="140"/>
+      <c r="I13" s="121"/>
+      <c r="J13" s="121"/>
       <c r="K13" s="7"/>
       <c r="L13" s="1"/>
       <c r="M13" s="1"/>
@@ -2370,10 +2369,10 @@
       <c r="C14" s="28" t="s">
         <v>21</v>
       </c>
-      <c r="D14" s="130">
+      <c r="D14" s="110">
         <v>45386</v>
       </c>
-      <c r="E14" s="131"/>
+      <c r="E14" s="111"/>
       <c r="F14" s="35"/>
       <c r="G14" s="26" t="s">
         <v>22</v>
@@ -2414,11 +2413,11 @@
       <c r="G15" s="26" t="s">
         <v>35</v>
       </c>
-      <c r="H15" s="110" t="s">
+      <c r="H15" s="138" t="s">
         <v>36</v>
       </c>
-      <c r="I15" s="111"/>
-      <c r="J15" s="111"/>
+      <c r="I15" s="113"/>
+      <c r="J15" s="113"/>
       <c r="K15" s="7"/>
       <c r="L15" s="1"/>
       <c r="M15" s="1"/>
@@ -2498,13 +2497,13 @@
       <c r="C18" s="49" t="s">
         <v>38</v>
       </c>
-      <c r="D18" s="112"/>
-      <c r="E18" s="113"/>
-      <c r="F18" s="113"/>
-      <c r="G18" s="113"/>
-      <c r="H18" s="113"/>
-      <c r="I18" s="113"/>
-      <c r="J18" s="114"/>
+      <c r="D18" s="139"/>
+      <c r="E18" s="140"/>
+      <c r="F18" s="140"/>
+      <c r="G18" s="140"/>
+      <c r="H18" s="140"/>
+      <c r="I18" s="140"/>
+      <c r="J18" s="141"/>
       <c r="K18" s="7"/>
       <c r="L18" s="1"/>
       <c r="M18" s="1"/>
@@ -2584,10 +2583,10 @@
       <c r="C21" s="57" t="s">
         <v>29</v>
       </c>
-      <c r="D21" s="132" t="s">
+      <c r="D21" s="112" t="s">
         <v>44</v>
       </c>
-      <c r="E21" s="111"/>
+      <c r="E21" s="113"/>
       <c r="F21" s="60" t="s">
         <v>46</v>
       </c>
@@ -2597,11 +2596,11 @@
       <c r="H21" s="62" t="s">
         <v>33</v>
       </c>
-      <c r="I21" s="115">
+      <c r="I21" s="142">
         <f>I57</f>
         <v>0</v>
       </c>
-      <c r="J21" s="111"/>
+      <c r="J21" s="113"/>
       <c r="K21" s="64" t="s">
         <v>37</v>
       </c>
@@ -2714,12 +2713,12 @@
       <c r="D25" s="70" t="s">
         <v>49</v>
       </c>
-      <c r="E25" s="116" t="s">
+      <c r="E25" s="143" t="s">
         <v>50</v>
       </c>
-      <c r="F25" s="117"/>
-      <c r="G25" s="117"/>
-      <c r="H25" s="118"/>
+      <c r="F25" s="144"/>
+      <c r="G25" s="144"/>
+      <c r="H25" s="145"/>
       <c r="I25" s="71" t="s">
         <v>51</v>
       </c>
@@ -2743,321 +2742,321 @@
       <c r="Y25" s="2"/>
       <c r="Z25" s="2"/>
     </row>
-    <row r="26" spans="1:26" s="167" customFormat="1" ht="30" customHeight="1">
-      <c r="C26" s="170"/>
-      <c r="D26" s="170"/>
-      <c r="E26" s="171"/>
-      <c r="F26" s="171"/>
-      <c r="G26" s="171"/>
-      <c r="H26" s="171"/>
-      <c r="I26" s="170"/>
-      <c r="J26" s="170"/>
-    </row>
-    <row r="27" spans="1:26" s="167" customFormat="1" ht="30" customHeight="1">
-      <c r="C27" s="170"/>
-      <c r="D27" s="170"/>
-      <c r="E27" s="171"/>
-      <c r="F27" s="171"/>
-      <c r="G27" s="171"/>
-      <c r="H27" s="171"/>
-      <c r="I27" s="170"/>
-      <c r="J27" s="170"/>
-    </row>
-    <row r="28" spans="1:26" s="167" customFormat="1" ht="30" customHeight="1">
-      <c r="C28" s="170"/>
-      <c r="D28" s="170"/>
-      <c r="E28" s="171"/>
-      <c r="F28" s="171"/>
-      <c r="G28" s="171"/>
-      <c r="H28" s="171"/>
-      <c r="I28" s="170"/>
-      <c r="J28" s="170"/>
-    </row>
-    <row r="29" spans="1:26" s="167" customFormat="1" ht="30" customHeight="1">
-      <c r="C29" s="170"/>
-      <c r="D29" s="170"/>
-      <c r="E29" s="171"/>
-      <c r="F29" s="171"/>
-      <c r="G29" s="171"/>
-      <c r="H29" s="171"/>
-      <c r="I29" s="170"/>
-      <c r="J29" s="170"/>
-    </row>
-    <row r="30" spans="1:26" s="167" customFormat="1" ht="30" customHeight="1">
-      <c r="C30" s="170"/>
-      <c r="D30" s="170"/>
-      <c r="E30" s="171"/>
-      <c r="F30" s="171"/>
-      <c r="G30" s="171"/>
-      <c r="H30" s="171"/>
-      <c r="I30" s="170"/>
-      <c r="J30" s="170"/>
-    </row>
-    <row r="31" spans="1:26" s="167" customFormat="1" ht="30" customHeight="1">
-      <c r="C31" s="170"/>
-      <c r="D31" s="170"/>
-      <c r="E31" s="171"/>
-      <c r="F31" s="171"/>
-      <c r="G31" s="171"/>
-      <c r="H31" s="171"/>
-      <c r="I31" s="170"/>
-      <c r="J31" s="170"/>
-    </row>
-    <row r="32" spans="1:26" s="167" customFormat="1" ht="30" customHeight="1">
-      <c r="C32" s="170"/>
-      <c r="D32" s="170"/>
-      <c r="E32" s="171"/>
-      <c r="F32" s="171"/>
-      <c r="G32" s="171"/>
-      <c r="H32" s="171"/>
-      <c r="I32" s="170"/>
-      <c r="J32" s="170"/>
-    </row>
-    <row r="33" spans="3:10" s="167" customFormat="1" ht="30" customHeight="1">
-      <c r="C33" s="170"/>
-      <c r="D33" s="170"/>
-      <c r="E33" s="171"/>
-      <c r="F33" s="171"/>
-      <c r="G33" s="171"/>
-      <c r="H33" s="171"/>
-      <c r="I33" s="170"/>
-      <c r="J33" s="170"/>
-    </row>
-    <row r="34" spans="3:10" s="167" customFormat="1" ht="30" customHeight="1">
-      <c r="C34" s="170"/>
-      <c r="D34" s="170"/>
-      <c r="E34" s="171"/>
-      <c r="F34" s="171"/>
-      <c r="G34" s="171"/>
-      <c r="H34" s="171"/>
-      <c r="I34" s="170"/>
-      <c r="J34" s="170"/>
-    </row>
-    <row r="35" spans="3:10" s="167" customFormat="1" ht="30" customHeight="1">
-      <c r="C35" s="170"/>
-      <c r="D35" s="170"/>
-      <c r="E35" s="171"/>
-      <c r="F35" s="171"/>
-      <c r="G35" s="171"/>
-      <c r="H35" s="171"/>
-      <c r="I35" s="170"/>
-      <c r="J35" s="170"/>
-    </row>
-    <row r="36" spans="3:10" s="167" customFormat="1" ht="30" customHeight="1">
-      <c r="C36" s="170"/>
-      <c r="D36" s="170"/>
-      <c r="E36" s="171"/>
-      <c r="F36" s="171"/>
-      <c r="G36" s="171"/>
-      <c r="H36" s="171"/>
-      <c r="I36" s="170"/>
-      <c r="J36" s="170"/>
-    </row>
-    <row r="37" spans="3:10" s="167" customFormat="1" ht="30" customHeight="1">
-      <c r="C37" s="170"/>
-      <c r="D37" s="170"/>
-      <c r="E37" s="171"/>
-      <c r="F37" s="171"/>
-      <c r="G37" s="171"/>
-      <c r="H37" s="171"/>
-      <c r="I37" s="170"/>
-      <c r="J37" s="170"/>
-    </row>
-    <row r="38" spans="3:10" s="167" customFormat="1" ht="30" customHeight="1">
-      <c r="C38" s="170"/>
-      <c r="D38" s="170"/>
-      <c r="E38" s="171"/>
-      <c r="F38" s="171"/>
-      <c r="G38" s="171"/>
-      <c r="H38" s="171"/>
-      <c r="I38" s="170"/>
-      <c r="J38" s="170"/>
-    </row>
-    <row r="39" spans="3:10" s="167" customFormat="1" ht="30" customHeight="1">
-      <c r="C39" s="170"/>
-      <c r="D39" s="170"/>
-      <c r="E39" s="171"/>
-      <c r="F39" s="171"/>
-      <c r="G39" s="171"/>
-      <c r="H39" s="171"/>
-      <c r="I39" s="170"/>
-      <c r="J39" s="170"/>
-    </row>
-    <row r="40" spans="3:10" s="167" customFormat="1" ht="30" customHeight="1">
-      <c r="C40" s="170"/>
-      <c r="D40" s="170"/>
-      <c r="E40" s="171"/>
-      <c r="F40" s="171"/>
-      <c r="G40" s="171"/>
-      <c r="H40" s="171"/>
-      <c r="I40" s="170"/>
-      <c r="J40" s="170"/>
-    </row>
-    <row r="41" spans="3:10" s="167" customFormat="1" ht="30" customHeight="1">
-      <c r="C41" s="170"/>
-      <c r="D41" s="170"/>
-      <c r="E41" s="171"/>
-      <c r="F41" s="171"/>
-      <c r="G41" s="171"/>
-      <c r="H41" s="171"/>
-      <c r="I41" s="170"/>
-      <c r="J41" s="170"/>
-    </row>
-    <row r="42" spans="3:10" s="167" customFormat="1" ht="30" customHeight="1">
-      <c r="C42" s="170"/>
-      <c r="D42" s="170"/>
-      <c r="E42" s="172"/>
-      <c r="F42" s="172"/>
-      <c r="G42" s="172"/>
-      <c r="H42" s="172"/>
-      <c r="I42" s="170"/>
-      <c r="J42" s="170"/>
-    </row>
-    <row r="43" spans="3:10" s="167" customFormat="1" ht="30" customHeight="1">
-      <c r="C43" s="170"/>
-      <c r="D43" s="170"/>
-      <c r="E43" s="172"/>
-      <c r="F43" s="172"/>
-      <c r="G43" s="172"/>
-      <c r="H43" s="172"/>
-      <c r="I43" s="170"/>
-      <c r="J43" s="170"/>
-    </row>
-    <row r="44" spans="3:10" s="167" customFormat="1" ht="30" customHeight="1">
-      <c r="C44" s="170"/>
-      <c r="D44" s="170"/>
-      <c r="E44" s="172"/>
-      <c r="F44" s="172"/>
-      <c r="G44" s="172"/>
-      <c r="H44" s="172"/>
-      <c r="I44" s="170"/>
-      <c r="J44" s="170"/>
-    </row>
-    <row r="45" spans="3:10" s="167" customFormat="1" ht="30" customHeight="1">
-      <c r="C45" s="170"/>
-      <c r="D45" s="170"/>
-      <c r="E45" s="172"/>
-      <c r="F45" s="172"/>
-      <c r="G45" s="172"/>
-      <c r="H45" s="172"/>
-      <c r="I45" s="170"/>
-      <c r="J45" s="170"/>
-    </row>
-    <row r="46" spans="3:10" s="167" customFormat="1" ht="30" customHeight="1">
-      <c r="C46" s="170"/>
-      <c r="D46" s="170"/>
-      <c r="E46" s="172"/>
-      <c r="F46" s="172"/>
-      <c r="G46" s="172"/>
-      <c r="H46" s="172"/>
-      <c r="I46" s="170"/>
-      <c r="J46" s="170"/>
-    </row>
-    <row r="47" spans="3:10" s="167" customFormat="1" ht="30" customHeight="1">
-      <c r="C47" s="170"/>
-      <c r="D47" s="170"/>
-      <c r="E47" s="172"/>
-      <c r="F47" s="172"/>
-      <c r="G47" s="172"/>
-      <c r="H47" s="172"/>
-      <c r="I47" s="170"/>
-      <c r="J47" s="170"/>
-    </row>
-    <row r="48" spans="3:10" s="167" customFormat="1" ht="30" customHeight="1">
-      <c r="C48" s="170"/>
-      <c r="D48" s="170"/>
-      <c r="E48" s="172"/>
-      <c r="F48" s="172"/>
-      <c r="G48" s="172"/>
-      <c r="H48" s="172"/>
-      <c r="I48" s="170"/>
-      <c r="J48" s="170"/>
-    </row>
-    <row r="49" spans="1:26" s="167" customFormat="1" ht="30" customHeight="1">
-      <c r="C49" s="170"/>
-      <c r="D49" s="170"/>
-      <c r="E49" s="172"/>
-      <c r="F49" s="172"/>
-      <c r="G49" s="172"/>
-      <c r="H49" s="172"/>
-      <c r="I49" s="170"/>
-      <c r="J49" s="170"/>
-    </row>
-    <row r="50" spans="1:26" s="167" customFormat="1" ht="30" customHeight="1">
-      <c r="C50" s="170"/>
-      <c r="D50" s="170"/>
-      <c r="E50" s="172"/>
-      <c r="F50" s="172"/>
-      <c r="G50" s="172"/>
-      <c r="H50" s="172"/>
-      <c r="I50" s="170"/>
-      <c r="J50" s="170"/>
-    </row>
-    <row r="51" spans="1:26" s="167" customFormat="1" ht="30" customHeight="1">
-      <c r="C51" s="170"/>
-      <c r="D51" s="170"/>
-      <c r="E51" s="172"/>
-      <c r="F51" s="172"/>
-      <c r="G51" s="172"/>
-      <c r="H51" s="172"/>
-      <c r="I51" s="170"/>
-      <c r="J51" s="170"/>
-    </row>
-    <row r="52" spans="1:26" s="167" customFormat="1" ht="30" customHeight="1">
-      <c r="C52" s="170"/>
-      <c r="D52" s="170"/>
-      <c r="E52" s="172"/>
-      <c r="F52" s="172"/>
-      <c r="G52" s="172"/>
-      <c r="H52" s="172"/>
-      <c r="I52" s="170"/>
-      <c r="J52" s="170"/>
-    </row>
-    <row r="53" spans="1:26" s="167" customFormat="1" ht="30" customHeight="1">
-      <c r="C53" s="170"/>
-      <c r="D53" s="170"/>
-      <c r="E53" s="172"/>
-      <c r="F53" s="172"/>
-      <c r="G53" s="172"/>
-      <c r="H53" s="172"/>
-      <c r="I53" s="170"/>
-      <c r="J53" s="170"/>
-    </row>
-    <row r="54" spans="1:26" s="167" customFormat="1" ht="30" customHeight="1">
-      <c r="C54" s="170"/>
-      <c r="D54" s="170"/>
-      <c r="E54" s="172"/>
-      <c r="F54" s="172"/>
-      <c r="G54" s="172"/>
-      <c r="H54" s="172"/>
-      <c r="I54" s="170"/>
-      <c r="J54" s="170"/>
-    </row>
-    <row r="55" spans="1:26" s="167" customFormat="1" ht="30" customHeight="1">
-      <c r="C55" s="170"/>
-      <c r="D55" s="170"/>
-      <c r="E55" s="172"/>
-      <c r="F55" s="172"/>
-      <c r="G55" s="172"/>
-      <c r="H55" s="172"/>
-      <c r="I55" s="170"/>
-      <c r="J55" s="170"/>
+    <row r="26" spans="1:26" s="103" customFormat="1" ht="30" customHeight="1">
+      <c r="C26" s="106"/>
+      <c r="D26" s="106"/>
+      <c r="E26" s="109"/>
+      <c r="F26" s="109"/>
+      <c r="G26" s="109"/>
+      <c r="H26" s="109"/>
+      <c r="I26" s="106"/>
+      <c r="J26" s="106"/>
+    </row>
+    <row r="27" spans="1:26" s="103" customFormat="1" ht="30" customHeight="1">
+      <c r="C27" s="106"/>
+      <c r="D27" s="106"/>
+      <c r="E27" s="109"/>
+      <c r="F27" s="109"/>
+      <c r="G27" s="109"/>
+      <c r="H27" s="109"/>
+      <c r="I27" s="106"/>
+      <c r="J27" s="106"/>
+    </row>
+    <row r="28" spans="1:26" s="103" customFormat="1" ht="30" customHeight="1">
+      <c r="C28" s="106"/>
+      <c r="D28" s="106"/>
+      <c r="E28" s="109"/>
+      <c r="F28" s="109"/>
+      <c r="G28" s="109"/>
+      <c r="H28" s="109"/>
+      <c r="I28" s="106"/>
+      <c r="J28" s="106"/>
+    </row>
+    <row r="29" spans="1:26" s="103" customFormat="1" ht="30" customHeight="1">
+      <c r="C29" s="106"/>
+      <c r="D29" s="106"/>
+      <c r="E29" s="109"/>
+      <c r="F29" s="109"/>
+      <c r="G29" s="109"/>
+      <c r="H29" s="109"/>
+      <c r="I29" s="106"/>
+      <c r="J29" s="106"/>
+    </row>
+    <row r="30" spans="1:26" s="103" customFormat="1" ht="30" customHeight="1">
+      <c r="C30" s="106"/>
+      <c r="D30" s="106"/>
+      <c r="E30" s="109"/>
+      <c r="F30" s="109"/>
+      <c r="G30" s="109"/>
+      <c r="H30" s="109"/>
+      <c r="I30" s="106"/>
+      <c r="J30" s="106"/>
+    </row>
+    <row r="31" spans="1:26" s="103" customFormat="1" ht="30" customHeight="1">
+      <c r="C31" s="106"/>
+      <c r="D31" s="106"/>
+      <c r="E31" s="109"/>
+      <c r="F31" s="109"/>
+      <c r="G31" s="109"/>
+      <c r="H31" s="109"/>
+      <c r="I31" s="106"/>
+      <c r="J31" s="106"/>
+    </row>
+    <row r="32" spans="1:26" s="103" customFormat="1" ht="30" customHeight="1">
+      <c r="C32" s="106"/>
+      <c r="D32" s="106"/>
+      <c r="E32" s="109"/>
+      <c r="F32" s="109"/>
+      <c r="G32" s="109"/>
+      <c r="H32" s="109"/>
+      <c r="I32" s="106"/>
+      <c r="J32" s="106"/>
+    </row>
+    <row r="33" spans="3:10" s="103" customFormat="1" ht="30" customHeight="1">
+      <c r="C33" s="106"/>
+      <c r="D33" s="106"/>
+      <c r="E33" s="109"/>
+      <c r="F33" s="109"/>
+      <c r="G33" s="109"/>
+      <c r="H33" s="109"/>
+      <c r="I33" s="106"/>
+      <c r="J33" s="106"/>
+    </row>
+    <row r="34" spans="3:10" s="103" customFormat="1" ht="30" customHeight="1">
+      <c r="C34" s="106"/>
+      <c r="D34" s="106"/>
+      <c r="E34" s="109"/>
+      <c r="F34" s="109"/>
+      <c r="G34" s="109"/>
+      <c r="H34" s="109"/>
+      <c r="I34" s="106"/>
+      <c r="J34" s="106"/>
+    </row>
+    <row r="35" spans="3:10" s="103" customFormat="1" ht="30" customHeight="1">
+      <c r="C35" s="106"/>
+      <c r="D35" s="106"/>
+      <c r="E35" s="109"/>
+      <c r="F35" s="109"/>
+      <c r="G35" s="109"/>
+      <c r="H35" s="109"/>
+      <c r="I35" s="106"/>
+      <c r="J35" s="106"/>
+    </row>
+    <row r="36" spans="3:10" s="103" customFormat="1" ht="30" customHeight="1">
+      <c r="C36" s="106"/>
+      <c r="D36" s="106"/>
+      <c r="E36" s="109"/>
+      <c r="F36" s="109"/>
+      <c r="G36" s="109"/>
+      <c r="H36" s="109"/>
+      <c r="I36" s="106"/>
+      <c r="J36" s="106"/>
+    </row>
+    <row r="37" spans="3:10" s="103" customFormat="1" ht="30" customHeight="1">
+      <c r="C37" s="106"/>
+      <c r="D37" s="106"/>
+      <c r="E37" s="109"/>
+      <c r="F37" s="109"/>
+      <c r="G37" s="109"/>
+      <c r="H37" s="109"/>
+      <c r="I37" s="106"/>
+      <c r="J37" s="106"/>
+    </row>
+    <row r="38" spans="3:10" s="103" customFormat="1" ht="30" customHeight="1">
+      <c r="C38" s="106"/>
+      <c r="D38" s="106"/>
+      <c r="E38" s="109"/>
+      <c r="F38" s="109"/>
+      <c r="G38" s="109"/>
+      <c r="H38" s="109"/>
+      <c r="I38" s="106"/>
+      <c r="J38" s="106"/>
+    </row>
+    <row r="39" spans="3:10" s="103" customFormat="1" ht="30" customHeight="1">
+      <c r="C39" s="106"/>
+      <c r="D39" s="106"/>
+      <c r="E39" s="109"/>
+      <c r="F39" s="109"/>
+      <c r="G39" s="109"/>
+      <c r="H39" s="109"/>
+      <c r="I39" s="106"/>
+      <c r="J39" s="106"/>
+    </row>
+    <row r="40" spans="3:10" s="103" customFormat="1" ht="30" customHeight="1">
+      <c r="C40" s="106"/>
+      <c r="D40" s="106"/>
+      <c r="E40" s="109"/>
+      <c r="F40" s="109"/>
+      <c r="G40" s="109"/>
+      <c r="H40" s="109"/>
+      <c r="I40" s="106"/>
+      <c r="J40" s="106"/>
+    </row>
+    <row r="41" spans="3:10" s="103" customFormat="1" ht="30" customHeight="1">
+      <c r="C41" s="106"/>
+      <c r="D41" s="106"/>
+      <c r="E41" s="109"/>
+      <c r="F41" s="109"/>
+      <c r="G41" s="109"/>
+      <c r="H41" s="109"/>
+      <c r="I41" s="106"/>
+      <c r="J41" s="106"/>
+    </row>
+    <row r="42" spans="3:10" s="103" customFormat="1" ht="30" customHeight="1">
+      <c r="C42" s="106"/>
+      <c r="D42" s="106"/>
+      <c r="E42" s="125"/>
+      <c r="F42" s="125"/>
+      <c r="G42" s="125"/>
+      <c r="H42" s="125"/>
+      <c r="I42" s="106"/>
+      <c r="J42" s="106"/>
+    </row>
+    <row r="43" spans="3:10" s="103" customFormat="1" ht="30" customHeight="1">
+      <c r="C43" s="106"/>
+      <c r="D43" s="106"/>
+      <c r="E43" s="125"/>
+      <c r="F43" s="125"/>
+      <c r="G43" s="125"/>
+      <c r="H43" s="125"/>
+      <c r="I43" s="106"/>
+      <c r="J43" s="106"/>
+    </row>
+    <row r="44" spans="3:10" s="103" customFormat="1" ht="30" customHeight="1">
+      <c r="C44" s="106"/>
+      <c r="D44" s="106"/>
+      <c r="E44" s="125"/>
+      <c r="F44" s="125"/>
+      <c r="G44" s="125"/>
+      <c r="H44" s="125"/>
+      <c r="I44" s="106"/>
+      <c r="J44" s="106"/>
+    </row>
+    <row r="45" spans="3:10" s="103" customFormat="1" ht="30" customHeight="1">
+      <c r="C45" s="106"/>
+      <c r="D45" s="106"/>
+      <c r="E45" s="125"/>
+      <c r="F45" s="125"/>
+      <c r="G45" s="125"/>
+      <c r="H45" s="125"/>
+      <c r="I45" s="106"/>
+      <c r="J45" s="106"/>
+    </row>
+    <row r="46" spans="3:10" s="103" customFormat="1" ht="30" customHeight="1">
+      <c r="C46" s="106"/>
+      <c r="D46" s="106"/>
+      <c r="E46" s="125"/>
+      <c r="F46" s="125"/>
+      <c r="G46" s="125"/>
+      <c r="H46" s="125"/>
+      <c r="I46" s="106"/>
+      <c r="J46" s="106"/>
+    </row>
+    <row r="47" spans="3:10" s="103" customFormat="1" ht="30" customHeight="1">
+      <c r="C47" s="106"/>
+      <c r="D47" s="106"/>
+      <c r="E47" s="125"/>
+      <c r="F47" s="125"/>
+      <c r="G47" s="125"/>
+      <c r="H47" s="125"/>
+      <c r="I47" s="106"/>
+      <c r="J47" s="106"/>
+    </row>
+    <row r="48" spans="3:10" s="103" customFormat="1" ht="30" customHeight="1">
+      <c r="C48" s="106"/>
+      <c r="D48" s="106"/>
+      <c r="E48" s="125"/>
+      <c r="F48" s="125"/>
+      <c r="G48" s="125"/>
+      <c r="H48" s="125"/>
+      <c r="I48" s="106"/>
+      <c r="J48" s="106"/>
+    </row>
+    <row r="49" spans="1:26" s="103" customFormat="1" ht="30" customHeight="1">
+      <c r="C49" s="106"/>
+      <c r="D49" s="106"/>
+      <c r="E49" s="125"/>
+      <c r="F49" s="125"/>
+      <c r="G49" s="125"/>
+      <c r="H49" s="125"/>
+      <c r="I49" s="106"/>
+      <c r="J49" s="106"/>
+    </row>
+    <row r="50" spans="1:26" s="103" customFormat="1" ht="30" customHeight="1">
+      <c r="C50" s="106"/>
+      <c r="D50" s="106"/>
+      <c r="E50" s="125"/>
+      <c r="F50" s="125"/>
+      <c r="G50" s="125"/>
+      <c r="H50" s="125"/>
+      <c r="I50" s="106"/>
+      <c r="J50" s="106"/>
+    </row>
+    <row r="51" spans="1:26" s="103" customFormat="1" ht="30" customHeight="1">
+      <c r="C51" s="106"/>
+      <c r="D51" s="106"/>
+      <c r="E51" s="125"/>
+      <c r="F51" s="125"/>
+      <c r="G51" s="125"/>
+      <c r="H51" s="125"/>
+      <c r="I51" s="106"/>
+      <c r="J51" s="106"/>
+    </row>
+    <row r="52" spans="1:26" s="103" customFormat="1" ht="30" customHeight="1">
+      <c r="C52" s="106"/>
+      <c r="D52" s="106"/>
+      <c r="E52" s="125"/>
+      <c r="F52" s="125"/>
+      <c r="G52" s="125"/>
+      <c r="H52" s="125"/>
+      <c r="I52" s="106"/>
+      <c r="J52" s="106"/>
+    </row>
+    <row r="53" spans="1:26" s="103" customFormat="1" ht="30" customHeight="1">
+      <c r="C53" s="106"/>
+      <c r="D53" s="106"/>
+      <c r="E53" s="125"/>
+      <c r="F53" s="125"/>
+      <c r="G53" s="125"/>
+      <c r="H53" s="125"/>
+      <c r="I53" s="106"/>
+      <c r="J53" s="106"/>
+    </row>
+    <row r="54" spans="1:26" s="103" customFormat="1" ht="30" customHeight="1">
+      <c r="C54" s="106"/>
+      <c r="D54" s="106"/>
+      <c r="E54" s="125"/>
+      <c r="F54" s="125"/>
+      <c r="G54" s="125"/>
+      <c r="H54" s="125"/>
+      <c r="I54" s="106"/>
+      <c r="J54" s="106"/>
+    </row>
+    <row r="55" spans="1:26" s="103" customFormat="1" ht="30" customHeight="1">
+      <c r="C55" s="106"/>
+      <c r="D55" s="106"/>
+      <c r="E55" s="125"/>
+      <c r="F55" s="125"/>
+      <c r="G55" s="125"/>
+      <c r="H55" s="125"/>
+      <c r="I55" s="106"/>
+      <c r="J55" s="106"/>
     </row>
     <row r="56" spans="1:26" ht="32.25" customHeight="1">
       <c r="A56" s="1"/>
       <c r="B56" s="12"/>
-      <c r="C56" s="173" t="s">
+      <c r="C56" s="107" t="s">
         <v>53</v>
       </c>
-      <c r="D56" s="174" t="s">
+      <c r="D56" s="126" t="s">
         <v>54</v>
       </c>
-      <c r="E56" s="175"/>
-      <c r="F56" s="175"/>
-      <c r="G56" s="175"/>
-      <c r="H56" s="175"/>
-      <c r="I56" s="176"/>
-      <c r="J56" s="173"/>
+      <c r="E56" s="127"/>
+      <c r="F56" s="127"/>
+      <c r="G56" s="127"/>
+      <c r="H56" s="127"/>
+      <c r="I56" s="108"/>
+      <c r="J56" s="107"/>
       <c r="K56" s="76"/>
       <c r="L56" s="1"/>
       <c r="M56" s="1"/>
@@ -3078,14 +3077,14 @@
     <row r="57" spans="1:26" ht="23.25" customHeight="1">
       <c r="A57" s="1"/>
       <c r="B57" s="1"/>
-      <c r="C57" s="126"/>
-      <c r="D57" s="127"/>
-      <c r="E57" s="128" t="s">
+      <c r="C57" s="128"/>
+      <c r="D57" s="129"/>
+      <c r="E57" s="130" t="s">
         <v>56</v>
       </c>
-      <c r="F57" s="129"/>
-      <c r="G57" s="129"/>
-      <c r="H57" s="127"/>
+      <c r="F57" s="131"/>
+      <c r="G57" s="131"/>
+      <c r="H57" s="129"/>
       <c r="I57" s="89">
         <f>SUM(I41:I56)</f>
         <v>0</v>
@@ -3138,16 +3137,16 @@
     </row>
     <row r="59" spans="1:26" ht="6" customHeight="1">
       <c r="A59" s="1"/>
-      <c r="B59" s="104"/>
-      <c r="C59" s="105"/>
-      <c r="D59" s="105"/>
-      <c r="E59" s="105"/>
-      <c r="F59" s="105"/>
-      <c r="G59" s="105"/>
-      <c r="H59" s="105"/>
-      <c r="I59" s="105"/>
-      <c r="J59" s="105"/>
-      <c r="K59" s="105"/>
+      <c r="B59" s="132"/>
+      <c r="C59" s="133"/>
+      <c r="D59" s="133"/>
+      <c r="E59" s="133"/>
+      <c r="F59" s="133"/>
+      <c r="G59" s="133"/>
+      <c r="H59" s="133"/>
+      <c r="I59" s="133"/>
+      <c r="J59" s="133"/>
+      <c r="K59" s="133"/>
       <c r="L59" s="1"/>
       <c r="M59" s="1"/>
       <c r="N59" s="1"/>
@@ -3166,17 +3165,17 @@
     </row>
     <row r="60" spans="1:26" ht="27" customHeight="1">
       <c r="A60" s="1"/>
-      <c r="B60" s="106" t="s">
+      <c r="B60" s="134" t="s">
         <v>58</v>
       </c>
-      <c r="C60" s="107"/>
-      <c r="D60" s="107"/>
-      <c r="E60" s="107"/>
-      <c r="F60" s="107"/>
-      <c r="G60" s="107"/>
-      <c r="H60" s="107"/>
-      <c r="I60" s="107"/>
-      <c r="J60" s="107"/>
+      <c r="C60" s="135"/>
+      <c r="D60" s="135"/>
+      <c r="E60" s="135"/>
+      <c r="F60" s="135"/>
+      <c r="G60" s="135"/>
+      <c r="H60" s="135"/>
+      <c r="I60" s="135"/>
+      <c r="J60" s="135"/>
       <c r="K60" s="7"/>
       <c r="L60" s="1"/>
       <c r="M60" s="1"/>
@@ -3196,15 +3195,15 @@
     </row>
     <row r="61" spans="1:26" ht="39" customHeight="1">
       <c r="A61" s="1"/>
-      <c r="B61" s="108"/>
-      <c r="C61" s="109"/>
-      <c r="D61" s="109"/>
-      <c r="E61" s="109"/>
-      <c r="F61" s="109"/>
-      <c r="G61" s="109"/>
-      <c r="H61" s="109"/>
-      <c r="I61" s="109"/>
-      <c r="J61" s="109"/>
+      <c r="B61" s="136"/>
+      <c r="C61" s="137"/>
+      <c r="D61" s="137"/>
+      <c r="E61" s="137"/>
+      <c r="F61" s="137"/>
+      <c r="G61" s="137"/>
+      <c r="H61" s="137"/>
+      <c r="I61" s="137"/>
+      <c r="J61" s="137"/>
       <c r="K61" s="7"/>
       <c r="L61" s="1"/>
       <c r="M61" s="1"/>
@@ -3224,15 +3223,15 @@
     </row>
     <row r="62" spans="1:26" ht="16.5" customHeight="1">
       <c r="A62" s="1"/>
-      <c r="B62" s="108"/>
-      <c r="C62" s="109"/>
-      <c r="D62" s="109"/>
-      <c r="E62" s="109"/>
-      <c r="F62" s="109"/>
-      <c r="G62" s="109"/>
-      <c r="H62" s="109"/>
-      <c r="I62" s="109"/>
-      <c r="J62" s="109"/>
+      <c r="B62" s="136"/>
+      <c r="C62" s="137"/>
+      <c r="D62" s="137"/>
+      <c r="E62" s="137"/>
+      <c r="F62" s="137"/>
+      <c r="G62" s="137"/>
+      <c r="H62" s="137"/>
+      <c r="I62" s="137"/>
+      <c r="J62" s="137"/>
       <c r="K62" s="7"/>
       <c r="L62" s="1"/>
       <c r="M62" s="1"/>
@@ -30020,40 +30019,6 @@
     </row>
   </sheetData>
   <mergeCells count="50">
-    <mergeCell ref="E26:H26"/>
-    <mergeCell ref="E31:H31"/>
-    <mergeCell ref="E30:H30"/>
-    <mergeCell ref="E29:H29"/>
-    <mergeCell ref="E28:H28"/>
-    <mergeCell ref="E27:H27"/>
-    <mergeCell ref="E35:H35"/>
-    <mergeCell ref="E34:H34"/>
-    <mergeCell ref="E33:H33"/>
-    <mergeCell ref="E36:H36"/>
-    <mergeCell ref="E32:H32"/>
-    <mergeCell ref="E40:H40"/>
-    <mergeCell ref="E39:H39"/>
-    <mergeCell ref="E38:H38"/>
-    <mergeCell ref="E37:H37"/>
-    <mergeCell ref="D14:E14"/>
-    <mergeCell ref="D21:E21"/>
-    <mergeCell ref="C7:D7"/>
-    <mergeCell ref="G7:H7"/>
-    <mergeCell ref="I7:J7"/>
-    <mergeCell ref="D9:F9"/>
-    <mergeCell ref="H9:J9"/>
-    <mergeCell ref="I12:I13"/>
-    <mergeCell ref="J12:J13"/>
-    <mergeCell ref="D12:E12"/>
-    <mergeCell ref="D13:E13"/>
-    <mergeCell ref="E44:H44"/>
-    <mergeCell ref="E55:H55"/>
-    <mergeCell ref="D56:H56"/>
-    <mergeCell ref="C57:D57"/>
-    <mergeCell ref="E57:H57"/>
-    <mergeCell ref="E46:H46"/>
-    <mergeCell ref="E47:H47"/>
-    <mergeCell ref="E48:H48"/>
     <mergeCell ref="B59:K59"/>
     <mergeCell ref="B60:J62"/>
     <mergeCell ref="H15:J15"/>
@@ -30070,6 +30035,40 @@
     <mergeCell ref="E52:H52"/>
     <mergeCell ref="E53:H53"/>
     <mergeCell ref="E54:H54"/>
+    <mergeCell ref="E55:H55"/>
+    <mergeCell ref="D56:H56"/>
+    <mergeCell ref="C57:D57"/>
+    <mergeCell ref="E57:H57"/>
+    <mergeCell ref="E46:H46"/>
+    <mergeCell ref="E47:H47"/>
+    <mergeCell ref="E48:H48"/>
+    <mergeCell ref="I12:I13"/>
+    <mergeCell ref="J12:J13"/>
+    <mergeCell ref="D12:E12"/>
+    <mergeCell ref="D13:E13"/>
+    <mergeCell ref="E44:H44"/>
+    <mergeCell ref="C7:D7"/>
+    <mergeCell ref="G7:H7"/>
+    <mergeCell ref="I7:J7"/>
+    <mergeCell ref="D9:F9"/>
+    <mergeCell ref="H9:J9"/>
+    <mergeCell ref="E40:H40"/>
+    <mergeCell ref="E39:H39"/>
+    <mergeCell ref="E38:H38"/>
+    <mergeCell ref="E37:H37"/>
+    <mergeCell ref="D14:E14"/>
+    <mergeCell ref="D21:E21"/>
+    <mergeCell ref="E35:H35"/>
+    <mergeCell ref="E34:H34"/>
+    <mergeCell ref="E33:H33"/>
+    <mergeCell ref="E36:H36"/>
+    <mergeCell ref="E32:H32"/>
+    <mergeCell ref="E26:H26"/>
+    <mergeCell ref="E31:H31"/>
+    <mergeCell ref="E30:H30"/>
+    <mergeCell ref="E29:H29"/>
+    <mergeCell ref="E28:H28"/>
+    <mergeCell ref="E27:H27"/>
   </mergeCells>
   <phoneticPr fontId="30" type="noConversion"/>
   <printOptions horizontalCentered="1" verticalCentered="1" gridLines="1"/>
@@ -30273,18 +30272,18 @@
     <row r="7" spans="1:26" ht="67.5" customHeight="1">
       <c r="A7" s="1"/>
       <c r="B7" s="1"/>
-      <c r="C7" s="133"/>
-      <c r="D7" s="111"/>
+      <c r="C7" s="114"/>
+      <c r="D7" s="113"/>
       <c r="E7" s="10" t="s">
         <v>1</v>
       </c>
       <c r="F7" s="10"/>
-      <c r="G7" s="134"/>
-      <c r="H7" s="111"/>
-      <c r="I7" s="135" t="s">
+      <c r="G7" s="115"/>
+      <c r="H7" s="113"/>
+      <c r="I7" s="116" t="s">
         <v>2</v>
       </c>
-      <c r="J7" s="111"/>
+      <c r="J7" s="113"/>
       <c r="K7" s="7"/>
       <c r="L7" s="1"/>
       <c r="M7" s="1"/>
@@ -30336,17 +30335,17 @@
       <c r="C9" s="14" t="s">
         <v>3</v>
       </c>
-      <c r="D9" s="136"/>
-      <c r="E9" s="137"/>
-      <c r="F9" s="137"/>
+      <c r="D9" s="117"/>
+      <c r="E9" s="118"/>
+      <c r="F9" s="118"/>
       <c r="G9" s="14" t="s">
         <v>6</v>
       </c>
-      <c r="H9" s="138" t="s">
+      <c r="H9" s="119" t="s">
         <v>8</v>
       </c>
-      <c r="I9" s="137"/>
-      <c r="J9" s="137"/>
+      <c r="I9" s="118"/>
+      <c r="J9" s="118"/>
       <c r="K9" s="7"/>
       <c r="L9" s="1"/>
       <c r="M9" s="2"/>
@@ -30426,8 +30425,8 @@
       <c r="C12" s="28" t="s">
         <v>7</v>
       </c>
-      <c r="D12" s="142"/>
-      <c r="E12" s="131"/>
+      <c r="D12" s="123"/>
+      <c r="E12" s="111"/>
       <c r="F12" s="30"/>
       <c r="G12" s="26" t="s">
         <v>9</v>
@@ -30462,8 +30461,8 @@
       <c r="A13" s="1"/>
       <c r="B13" s="12"/>
       <c r="C13" s="28"/>
-      <c r="D13" s="143"/>
-      <c r="E13" s="131"/>
+      <c r="D13" s="124"/>
+      <c r="E13" s="111"/>
       <c r="F13" s="35"/>
       <c r="G13" s="26" t="s">
         <v>17</v>
@@ -30500,8 +30499,8 @@
       <c r="C14" s="28" t="s">
         <v>21</v>
       </c>
-      <c r="D14" s="130"/>
-      <c r="E14" s="131"/>
+      <c r="D14" s="110"/>
+      <c r="E14" s="111"/>
       <c r="F14" s="35"/>
       <c r="G14" s="26" t="s">
         <v>22</v>
@@ -30542,11 +30541,11 @@
       <c r="G15" s="26" t="s">
         <v>35</v>
       </c>
-      <c r="H15" s="110" t="s">
+      <c r="H15" s="138" t="s">
         <v>36</v>
       </c>
-      <c r="I15" s="111"/>
-      <c r="J15" s="111"/>
+      <c r="I15" s="113"/>
+      <c r="J15" s="113"/>
       <c r="K15" s="7"/>
       <c r="L15" s="1"/>
       <c r="M15" s="1"/>
@@ -30626,13 +30625,13 @@
       <c r="C18" s="49" t="s">
         <v>38</v>
       </c>
-      <c r="D18" s="112"/>
-      <c r="E18" s="113"/>
-      <c r="F18" s="113"/>
-      <c r="G18" s="113"/>
-      <c r="H18" s="113"/>
-      <c r="I18" s="113"/>
-      <c r="J18" s="114"/>
+      <c r="D18" s="139"/>
+      <c r="E18" s="140"/>
+      <c r="F18" s="140"/>
+      <c r="G18" s="140"/>
+      <c r="H18" s="140"/>
+      <c r="I18" s="140"/>
+      <c r="J18" s="141"/>
       <c r="K18" s="7"/>
       <c r="L18" s="1"/>
       <c r="M18" s="1"/>
@@ -30712,10 +30711,10 @@
       <c r="C21" s="57" t="s">
         <v>29</v>
       </c>
-      <c r="D21" s="132" t="s">
+      <c r="D21" s="112" t="s">
         <v>45</v>
       </c>
-      <c r="E21" s="111"/>
+      <c r="E21" s="113"/>
       <c r="F21" s="60" t="s">
         <v>46</v>
       </c>
@@ -30725,11 +30724,11 @@
       <c r="H21" s="62" t="s">
         <v>33</v>
       </c>
-      <c r="I21" s="115">
+      <c r="I21" s="142">
         <f ca="1">I56</f>
         <v>0</v>
       </c>
-      <c r="J21" s="111"/>
+      <c r="J21" s="113"/>
       <c r="K21" s="64" t="s">
         <v>37</v>
       </c>
@@ -30842,12 +30841,12 @@
       <c r="D25" s="70" t="s">
         <v>49</v>
       </c>
-      <c r="E25" s="116" t="s">
+      <c r="E25" s="143" t="s">
         <v>50</v>
       </c>
-      <c r="F25" s="117"/>
-      <c r="G25" s="117"/>
-      <c r="H25" s="118"/>
+      <c r="F25" s="144"/>
+      <c r="G25" s="144"/>
+      <c r="H25" s="145"/>
       <c r="I25" s="71" t="s">
         <v>51</v>
       </c>
@@ -30876,10 +30875,10 @@
       <c r="B26" s="12"/>
       <c r="C26" s="72"/>
       <c r="D26" s="73"/>
-      <c r="E26" s="119"/>
-      <c r="F26" s="120"/>
-      <c r="G26" s="120"/>
-      <c r="H26" s="121"/>
+      <c r="E26" s="146"/>
+      <c r="F26" s="149"/>
+      <c r="G26" s="149"/>
+      <c r="H26" s="150"/>
       <c r="I26" s="74"/>
       <c r="J26" s="75"/>
       <c r="K26" s="76"/>
@@ -30902,12 +30901,12 @@
     <row r="27" spans="1:26" s="99" customFormat="1" ht="30" customHeight="1">
       <c r="A27" s="97"/>
       <c r="B27" s="97"/>
-      <c r="C27" s="168"/>
-      <c r="D27" s="169"/>
-      <c r="E27" s="119"/>
-      <c r="F27" s="144"/>
-      <c r="G27" s="144"/>
-      <c r="H27" s="145"/>
+      <c r="C27" s="104"/>
+      <c r="D27" s="105"/>
+      <c r="E27" s="146"/>
+      <c r="F27" s="147"/>
+      <c r="G27" s="147"/>
+      <c r="H27" s="148"/>
       <c r="I27" s="74"/>
       <c r="J27" s="75"/>
       <c r="K27" s="98"/>
@@ -30930,12 +30929,12 @@
     <row r="28" spans="1:26" s="99" customFormat="1" ht="30" customHeight="1">
       <c r="A28" s="97"/>
       <c r="B28" s="97"/>
-      <c r="C28" s="168"/>
-      <c r="D28" s="169"/>
-      <c r="E28" s="119"/>
-      <c r="F28" s="144"/>
-      <c r="G28" s="144"/>
-      <c r="H28" s="145"/>
+      <c r="C28" s="104"/>
+      <c r="D28" s="105"/>
+      <c r="E28" s="146"/>
+      <c r="F28" s="147"/>
+      <c r="G28" s="147"/>
+      <c r="H28" s="148"/>
       <c r="I28" s="74"/>
       <c r="J28" s="75"/>
       <c r="K28" s="98"/>
@@ -30958,12 +30957,12 @@
     <row r="29" spans="1:26" s="99" customFormat="1" ht="30" customHeight="1">
       <c r="A29" s="97"/>
       <c r="B29" s="97"/>
-      <c r="C29" s="168"/>
-      <c r="D29" s="169"/>
-      <c r="E29" s="119"/>
-      <c r="F29" s="144"/>
-      <c r="G29" s="144"/>
-      <c r="H29" s="145"/>
+      <c r="C29" s="104"/>
+      <c r="D29" s="105"/>
+      <c r="E29" s="146"/>
+      <c r="F29" s="147"/>
+      <c r="G29" s="147"/>
+      <c r="H29" s="148"/>
       <c r="I29" s="74"/>
       <c r="J29" s="75"/>
       <c r="K29" s="98"/>
@@ -30986,12 +30985,12 @@
     <row r="30" spans="1:26" s="99" customFormat="1" ht="30" customHeight="1">
       <c r="A30" s="97"/>
       <c r="B30" s="97"/>
-      <c r="C30" s="168"/>
-      <c r="D30" s="169"/>
-      <c r="E30" s="119"/>
-      <c r="F30" s="144"/>
-      <c r="G30" s="144"/>
-      <c r="H30" s="145"/>
+      <c r="C30" s="104"/>
+      <c r="D30" s="105"/>
+      <c r="E30" s="146"/>
+      <c r="F30" s="147"/>
+      <c r="G30" s="147"/>
+      <c r="H30" s="148"/>
       <c r="I30" s="74"/>
       <c r="J30" s="75"/>
       <c r="K30" s="98"/>
@@ -31014,12 +31013,12 @@
     <row r="31" spans="1:26" s="99" customFormat="1" ht="30" customHeight="1">
       <c r="A31" s="97"/>
       <c r="B31" s="97"/>
-      <c r="C31" s="168"/>
-      <c r="D31" s="169"/>
-      <c r="E31" s="119"/>
-      <c r="F31" s="144"/>
-      <c r="G31" s="144"/>
-      <c r="H31" s="145"/>
+      <c r="C31" s="104"/>
+      <c r="D31" s="105"/>
+      <c r="E31" s="146"/>
+      <c r="F31" s="147"/>
+      <c r="G31" s="147"/>
+      <c r="H31" s="148"/>
       <c r="I31" s="74"/>
       <c r="J31" s="75"/>
       <c r="K31" s="98"/>
@@ -31042,12 +31041,12 @@
     <row r="32" spans="1:26" s="99" customFormat="1" ht="30" customHeight="1">
       <c r="A32" s="97"/>
       <c r="B32" s="97"/>
-      <c r="C32" s="168"/>
-      <c r="D32" s="169"/>
-      <c r="E32" s="119"/>
-      <c r="F32" s="144"/>
-      <c r="G32" s="144"/>
-      <c r="H32" s="145"/>
+      <c r="C32" s="104"/>
+      <c r="D32" s="105"/>
+      <c r="E32" s="146"/>
+      <c r="F32" s="147"/>
+      <c r="G32" s="147"/>
+      <c r="H32" s="148"/>
       <c r="I32" s="74"/>
       <c r="J32" s="75"/>
       <c r="K32" s="98"/>
@@ -31070,12 +31069,12 @@
     <row r="33" spans="1:26" s="99" customFormat="1" ht="30" customHeight="1">
       <c r="A33" s="97"/>
       <c r="B33" s="97"/>
-      <c r="C33" s="168"/>
-      <c r="D33" s="169"/>
-      <c r="E33" s="119"/>
-      <c r="F33" s="144"/>
-      <c r="G33" s="144"/>
-      <c r="H33" s="145"/>
+      <c r="C33" s="104"/>
+      <c r="D33" s="105"/>
+      <c r="E33" s="146"/>
+      <c r="F33" s="147"/>
+      <c r="G33" s="147"/>
+      <c r="H33" s="148"/>
       <c r="I33" s="74"/>
       <c r="J33" s="75"/>
       <c r="K33" s="98"/>
@@ -31098,12 +31097,12 @@
     <row r="34" spans="1:26" s="99" customFormat="1" ht="30" customHeight="1">
       <c r="A34" s="97"/>
       <c r="B34" s="97"/>
-      <c r="C34" s="168"/>
-      <c r="D34" s="169"/>
-      <c r="E34" s="119"/>
-      <c r="F34" s="144"/>
-      <c r="G34" s="144"/>
-      <c r="H34" s="145"/>
+      <c r="C34" s="104"/>
+      <c r="D34" s="105"/>
+      <c r="E34" s="146"/>
+      <c r="F34" s="147"/>
+      <c r="G34" s="147"/>
+      <c r="H34" s="148"/>
       <c r="I34" s="74"/>
       <c r="J34" s="75"/>
       <c r="K34" s="98"/>
@@ -31126,12 +31125,12 @@
     <row r="35" spans="1:26" s="99" customFormat="1" ht="30" customHeight="1">
       <c r="A35" s="97"/>
       <c r="B35" s="97"/>
-      <c r="C35" s="168"/>
-      <c r="D35" s="169"/>
-      <c r="E35" s="119"/>
-      <c r="F35" s="144"/>
-      <c r="G35" s="144"/>
-      <c r="H35" s="145"/>
+      <c r="C35" s="104"/>
+      <c r="D35" s="105"/>
+      <c r="E35" s="146"/>
+      <c r="F35" s="147"/>
+      <c r="G35" s="147"/>
+      <c r="H35" s="148"/>
       <c r="I35" s="74"/>
       <c r="J35" s="75"/>
       <c r="K35" s="98"/>
@@ -31154,12 +31153,12 @@
     <row r="36" spans="1:26" s="99" customFormat="1" ht="30" customHeight="1">
       <c r="A36" s="97"/>
       <c r="B36" s="97"/>
-      <c r="C36" s="168"/>
-      <c r="D36" s="169"/>
-      <c r="E36" s="119"/>
-      <c r="F36" s="144"/>
-      <c r="G36" s="144"/>
-      <c r="H36" s="145"/>
+      <c r="C36" s="104"/>
+      <c r="D36" s="105"/>
+      <c r="E36" s="146"/>
+      <c r="F36" s="147"/>
+      <c r="G36" s="147"/>
+      <c r="H36" s="148"/>
       <c r="I36" s="74"/>
       <c r="J36" s="75"/>
       <c r="K36" s="98"/>
@@ -31182,12 +31181,12 @@
     <row r="37" spans="1:26" s="99" customFormat="1" ht="30" customHeight="1">
       <c r="A37" s="97"/>
       <c r="B37" s="97"/>
-      <c r="C37" s="168"/>
-      <c r="D37" s="169"/>
-      <c r="E37" s="119"/>
-      <c r="F37" s="144"/>
-      <c r="G37" s="144"/>
-      <c r="H37" s="145"/>
+      <c r="C37" s="104"/>
+      <c r="D37" s="105"/>
+      <c r="E37" s="146"/>
+      <c r="F37" s="147"/>
+      <c r="G37" s="147"/>
+      <c r="H37" s="148"/>
       <c r="I37" s="74"/>
       <c r="J37" s="75"/>
       <c r="K37" s="98"/>
@@ -31210,12 +31209,12 @@
     <row r="38" spans="1:26" s="99" customFormat="1" ht="30" customHeight="1">
       <c r="A38" s="97"/>
       <c r="B38" s="97"/>
-      <c r="C38" s="168"/>
-      <c r="D38" s="169"/>
-      <c r="E38" s="119"/>
-      <c r="F38" s="144"/>
-      <c r="G38" s="144"/>
-      <c r="H38" s="145"/>
+      <c r="C38" s="104"/>
+      <c r="D38" s="105"/>
+      <c r="E38" s="146"/>
+      <c r="F38" s="147"/>
+      <c r="G38" s="147"/>
+      <c r="H38" s="148"/>
       <c r="I38" s="74"/>
       <c r="J38" s="75"/>
       <c r="K38" s="98"/>
@@ -31238,12 +31237,12 @@
     <row r="39" spans="1:26" s="99" customFormat="1" ht="30" customHeight="1">
       <c r="A39" s="97"/>
       <c r="B39" s="97"/>
-      <c r="C39" s="168"/>
-      <c r="D39" s="169"/>
-      <c r="E39" s="119"/>
-      <c r="F39" s="144"/>
-      <c r="G39" s="144"/>
-      <c r="H39" s="145"/>
+      <c r="C39" s="104"/>
+      <c r="D39" s="105"/>
+      <c r="E39" s="146"/>
+      <c r="F39" s="147"/>
+      <c r="G39" s="147"/>
+      <c r="H39" s="148"/>
       <c r="I39" s="74"/>
       <c r="J39" s="75"/>
       <c r="K39" s="98"/>
@@ -31266,12 +31265,12 @@
     <row r="40" spans="1:26" s="99" customFormat="1" ht="30" customHeight="1">
       <c r="A40" s="97"/>
       <c r="B40" s="97"/>
-      <c r="C40" s="168"/>
-      <c r="D40" s="169"/>
-      <c r="E40" s="119"/>
-      <c r="F40" s="144"/>
-      <c r="G40" s="144"/>
-      <c r="H40" s="145"/>
+      <c r="C40" s="104"/>
+      <c r="D40" s="105"/>
+      <c r="E40" s="146"/>
+      <c r="F40" s="147"/>
+      <c r="G40" s="147"/>
+      <c r="H40" s="148"/>
       <c r="I40" s="74"/>
       <c r="J40" s="75"/>
       <c r="K40" s="98"/>
@@ -31296,10 +31295,10 @@
       <c r="B41" s="12"/>
       <c r="C41" s="79"/>
       <c r="D41" s="80"/>
-      <c r="E41" s="119"/>
-      <c r="F41" s="120"/>
-      <c r="G41" s="120"/>
-      <c r="H41" s="121"/>
+      <c r="E41" s="146"/>
+      <c r="F41" s="149"/>
+      <c r="G41" s="149"/>
+      <c r="H41" s="150"/>
       <c r="I41" s="81"/>
       <c r="J41" s="82"/>
       <c r="K41" s="76"/>
@@ -31324,10 +31323,10 @@
       <c r="B42" s="97"/>
       <c r="C42" s="79"/>
       <c r="D42" s="80"/>
-      <c r="E42" s="119"/>
-      <c r="F42" s="144"/>
-      <c r="G42" s="144"/>
-      <c r="H42" s="145"/>
+      <c r="E42" s="146"/>
+      <c r="F42" s="147"/>
+      <c r="G42" s="147"/>
+      <c r="H42" s="148"/>
       <c r="I42" s="81"/>
       <c r="J42" s="82"/>
       <c r="K42" s="98"/>
@@ -31352,10 +31351,10 @@
       <c r="B43" s="97"/>
       <c r="C43" s="79"/>
       <c r="D43" s="80"/>
-      <c r="E43" s="119"/>
-      <c r="F43" s="144"/>
-      <c r="G43" s="144"/>
-      <c r="H43" s="145"/>
+      <c r="E43" s="146"/>
+      <c r="F43" s="147"/>
+      <c r="G43" s="147"/>
+      <c r="H43" s="148"/>
       <c r="I43" s="81"/>
       <c r="J43" s="82"/>
       <c r="K43" s="98"/>
@@ -31380,10 +31379,10 @@
       <c r="B44" s="97"/>
       <c r="C44" s="79"/>
       <c r="D44" s="80"/>
-      <c r="E44" s="119"/>
-      <c r="F44" s="144"/>
-      <c r="G44" s="144"/>
-      <c r="H44" s="145"/>
+      <c r="E44" s="146"/>
+      <c r="F44" s="147"/>
+      <c r="G44" s="147"/>
+      <c r="H44" s="148"/>
       <c r="I44" s="81"/>
       <c r="J44" s="82"/>
       <c r="K44" s="98"/>
@@ -31408,10 +31407,10 @@
       <c r="B45" s="97"/>
       <c r="C45" s="79"/>
       <c r="D45" s="80"/>
-      <c r="E45" s="119"/>
-      <c r="F45" s="144"/>
-      <c r="G45" s="144"/>
-      <c r="H45" s="145"/>
+      <c r="E45" s="146"/>
+      <c r="F45" s="147"/>
+      <c r="G45" s="147"/>
+      <c r="H45" s="148"/>
       <c r="I45" s="81"/>
       <c r="J45" s="82"/>
       <c r="K45" s="98"/>
@@ -31436,10 +31435,10 @@
       <c r="B46" s="97"/>
       <c r="C46" s="79"/>
       <c r="D46" s="80"/>
-      <c r="E46" s="119"/>
-      <c r="F46" s="144"/>
-      <c r="G46" s="144"/>
-      <c r="H46" s="145"/>
+      <c r="E46" s="146"/>
+      <c r="F46" s="147"/>
+      <c r="G46" s="147"/>
+      <c r="H46" s="148"/>
       <c r="I46" s="81"/>
       <c r="J46" s="82"/>
       <c r="K46" s="98"/>
@@ -31464,10 +31463,10 @@
       <c r="B47" s="97"/>
       <c r="C47" s="79"/>
       <c r="D47" s="80"/>
-      <c r="E47" s="119"/>
-      <c r="F47" s="144"/>
-      <c r="G47" s="144"/>
-      <c r="H47" s="145"/>
+      <c r="E47" s="146"/>
+      <c r="F47" s="147"/>
+      <c r="G47" s="147"/>
+      <c r="H47" s="148"/>
       <c r="I47" s="81"/>
       <c r="J47" s="82"/>
       <c r="K47" s="98"/>
@@ -31492,10 +31491,10 @@
       <c r="B48" s="97"/>
       <c r="C48" s="79"/>
       <c r="D48" s="80"/>
-      <c r="E48" s="119"/>
-      <c r="F48" s="144"/>
-      <c r="G48" s="144"/>
-      <c r="H48" s="145"/>
+      <c r="E48" s="146"/>
+      <c r="F48" s="147"/>
+      <c r="G48" s="147"/>
+      <c r="H48" s="148"/>
       <c r="I48" s="81"/>
       <c r="J48" s="82"/>
       <c r="K48" s="98"/>
@@ -31520,10 +31519,10 @@
       <c r="B49" s="97"/>
       <c r="C49" s="79"/>
       <c r="D49" s="80"/>
-      <c r="E49" s="119"/>
-      <c r="F49" s="144"/>
-      <c r="G49" s="144"/>
-      <c r="H49" s="145"/>
+      <c r="E49" s="146"/>
+      <c r="F49" s="147"/>
+      <c r="G49" s="147"/>
+      <c r="H49" s="148"/>
       <c r="I49" s="81"/>
       <c r="J49" s="82"/>
       <c r="K49" s="98"/>
@@ -31548,10 +31547,10 @@
       <c r="B50" s="97"/>
       <c r="C50" s="79"/>
       <c r="D50" s="80"/>
-      <c r="E50" s="119"/>
-      <c r="F50" s="144"/>
-      <c r="G50" s="144"/>
-      <c r="H50" s="145"/>
+      <c r="E50" s="146"/>
+      <c r="F50" s="147"/>
+      <c r="G50" s="147"/>
+      <c r="H50" s="148"/>
       <c r="I50" s="81"/>
       <c r="J50" s="82"/>
       <c r="K50" s="98"/>
@@ -31576,10 +31575,10 @@
       <c r="B51" s="97"/>
       <c r="C51" s="79"/>
       <c r="D51" s="80"/>
-      <c r="E51" s="119"/>
-      <c r="F51" s="144"/>
-      <c r="G51" s="144"/>
-      <c r="H51" s="145"/>
+      <c r="E51" s="146"/>
+      <c r="F51" s="147"/>
+      <c r="G51" s="147"/>
+      <c r="H51" s="148"/>
       <c r="I51" s="81"/>
       <c r="J51" s="82"/>
       <c r="K51" s="98"/>
@@ -31604,10 +31603,10 @@
       <c r="B52" s="12"/>
       <c r="C52" s="77"/>
       <c r="D52" s="78"/>
-      <c r="E52" s="119"/>
-      <c r="F52" s="120"/>
-      <c r="G52" s="120"/>
-      <c r="H52" s="121"/>
+      <c r="E52" s="146"/>
+      <c r="F52" s="149"/>
+      <c r="G52" s="149"/>
+      <c r="H52" s="150"/>
       <c r="I52" s="81"/>
       <c r="J52" s="82"/>
       <c r="K52" s="76"/>
@@ -31632,10 +31631,10 @@
       <c r="B53" s="12"/>
       <c r="C53" s="83"/>
       <c r="D53" s="84"/>
-      <c r="E53" s="122"/>
-      <c r="F53" s="120"/>
-      <c r="G53" s="120"/>
-      <c r="H53" s="121"/>
+      <c r="E53" s="151"/>
+      <c r="F53" s="149"/>
+      <c r="G53" s="149"/>
+      <c r="H53" s="150"/>
       <c r="I53" s="85"/>
       <c r="J53" s="82"/>
       <c r="K53" s="76"/>
@@ -31660,10 +31659,10 @@
       <c r="B54" s="12"/>
       <c r="C54" s="77"/>
       <c r="D54" s="78"/>
-      <c r="E54" s="122"/>
-      <c r="F54" s="120"/>
-      <c r="G54" s="120"/>
-      <c r="H54" s="121"/>
+      <c r="E54" s="151"/>
+      <c r="F54" s="149"/>
+      <c r="G54" s="149"/>
+      <c r="H54" s="150"/>
       <c r="I54" s="81"/>
       <c r="J54" s="82"/>
       <c r="K54" s="76"/>
@@ -31689,13 +31688,13 @@
       <c r="C55" s="86" t="s">
         <v>53</v>
       </c>
-      <c r="D55" s="123" t="s">
+      <c r="D55" s="152" t="s">
         <v>54</v>
       </c>
-      <c r="E55" s="124"/>
-      <c r="F55" s="124"/>
-      <c r="G55" s="124"/>
-      <c r="H55" s="125"/>
+      <c r="E55" s="153"/>
+      <c r="F55" s="153"/>
+      <c r="G55" s="153"/>
+      <c r="H55" s="154"/>
       <c r="I55" s="88">
         <f ca="1">I55*0.1</f>
         <v>0</v>
@@ -31721,14 +31720,14 @@
     <row r="56" spans="1:26" ht="23.25" customHeight="1">
       <c r="A56" s="1"/>
       <c r="B56" s="1"/>
-      <c r="C56" s="126"/>
-      <c r="D56" s="127"/>
-      <c r="E56" s="128" t="s">
+      <c r="C56" s="128"/>
+      <c r="D56" s="129"/>
+      <c r="E56" s="130" t="s">
         <v>56</v>
       </c>
-      <c r="F56" s="129"/>
-      <c r="G56" s="129"/>
-      <c r="H56" s="127"/>
+      <c r="F56" s="131"/>
+      <c r="G56" s="131"/>
+      <c r="H56" s="129"/>
       <c r="I56" s="89">
         <f ca="1">SUM(I26:I55)</f>
         <v>0</v>
@@ -31781,16 +31780,16 @@
     </row>
     <row r="58" spans="1:26" ht="6" customHeight="1">
       <c r="A58" s="1"/>
-      <c r="B58" s="104"/>
-      <c r="C58" s="105"/>
-      <c r="D58" s="105"/>
-      <c r="E58" s="105"/>
-      <c r="F58" s="105"/>
-      <c r="G58" s="105"/>
-      <c r="H58" s="105"/>
-      <c r="I58" s="105"/>
-      <c r="J58" s="105"/>
-      <c r="K58" s="105"/>
+      <c r="B58" s="132"/>
+      <c r="C58" s="133"/>
+      <c r="D58" s="133"/>
+      <c r="E58" s="133"/>
+      <c r="F58" s="133"/>
+      <c r="G58" s="133"/>
+      <c r="H58" s="133"/>
+      <c r="I58" s="133"/>
+      <c r="J58" s="133"/>
+      <c r="K58" s="133"/>
       <c r="L58" s="1"/>
       <c r="M58" s="1"/>
       <c r="N58" s="1"/>
@@ -31809,17 +31808,17 @@
     </row>
     <row r="59" spans="1:26" ht="27" customHeight="1">
       <c r="A59" s="1"/>
-      <c r="B59" s="106" t="s">
+      <c r="B59" s="134" t="s">
         <v>58</v>
       </c>
-      <c r="C59" s="107"/>
-      <c r="D59" s="107"/>
-      <c r="E59" s="107"/>
-      <c r="F59" s="107"/>
-      <c r="G59" s="107"/>
-      <c r="H59" s="107"/>
-      <c r="I59" s="107"/>
-      <c r="J59" s="107"/>
+      <c r="C59" s="135"/>
+      <c r="D59" s="135"/>
+      <c r="E59" s="135"/>
+      <c r="F59" s="135"/>
+      <c r="G59" s="135"/>
+      <c r="H59" s="135"/>
+      <c r="I59" s="135"/>
+      <c r="J59" s="135"/>
       <c r="K59" s="7"/>
       <c r="L59" s="1"/>
       <c r="M59" s="1"/>
@@ -31839,15 +31838,15 @@
     </row>
     <row r="60" spans="1:26" ht="39" customHeight="1">
       <c r="A60" s="1"/>
-      <c r="B60" s="108"/>
-      <c r="C60" s="109"/>
-      <c r="D60" s="109"/>
-      <c r="E60" s="109"/>
-      <c r="F60" s="109"/>
-      <c r="G60" s="109"/>
-      <c r="H60" s="109"/>
-      <c r="I60" s="109"/>
-      <c r="J60" s="109"/>
+      <c r="B60" s="136"/>
+      <c r="C60" s="137"/>
+      <c r="D60" s="137"/>
+      <c r="E60" s="137"/>
+      <c r="F60" s="137"/>
+      <c r="G60" s="137"/>
+      <c r="H60" s="137"/>
+      <c r="I60" s="137"/>
+      <c r="J60" s="137"/>
       <c r="K60" s="7"/>
       <c r="L60" s="1"/>
       <c r="M60" s="1"/>
@@ -31867,15 +31866,15 @@
     </row>
     <row r="61" spans="1:26" ht="16.5" customHeight="1">
       <c r="A61" s="1"/>
-      <c r="B61" s="108"/>
-      <c r="C61" s="109"/>
-      <c r="D61" s="109"/>
-      <c r="E61" s="109"/>
-      <c r="F61" s="109"/>
-      <c r="G61" s="109"/>
-      <c r="H61" s="109"/>
-      <c r="I61" s="109"/>
-      <c r="J61" s="109"/>
+      <c r="B61" s="136"/>
+      <c r="C61" s="137"/>
+      <c r="D61" s="137"/>
+      <c r="E61" s="137"/>
+      <c r="F61" s="137"/>
+      <c r="G61" s="137"/>
+      <c r="H61" s="137"/>
+      <c r="I61" s="137"/>
+      <c r="J61" s="137"/>
       <c r="K61" s="7"/>
       <c r="L61" s="1"/>
       <c r="M61" s="1"/>
@@ -58663,37 +58662,6 @@
     </row>
   </sheetData>
   <mergeCells count="47">
-    <mergeCell ref="E40:H40"/>
-    <mergeCell ref="E34:H34"/>
-    <mergeCell ref="E36:H36"/>
-    <mergeCell ref="E37:H37"/>
-    <mergeCell ref="E38:H38"/>
-    <mergeCell ref="E39:H39"/>
-    <mergeCell ref="C7:D7"/>
-    <mergeCell ref="G7:H7"/>
-    <mergeCell ref="I7:J7"/>
-    <mergeCell ref="D9:F9"/>
-    <mergeCell ref="H9:J9"/>
-    <mergeCell ref="D12:E12"/>
-    <mergeCell ref="D13:E13"/>
-    <mergeCell ref="D14:E14"/>
-    <mergeCell ref="H15:J15"/>
-    <mergeCell ref="D18:J18"/>
-    <mergeCell ref="D21:E21"/>
-    <mergeCell ref="I21:J21"/>
-    <mergeCell ref="E25:H25"/>
-    <mergeCell ref="E26:H26"/>
-    <mergeCell ref="B58:K58"/>
-    <mergeCell ref="E50:H50"/>
-    <mergeCell ref="E51:H51"/>
-    <mergeCell ref="E27:H27"/>
-    <mergeCell ref="E28:H28"/>
-    <mergeCell ref="E29:H29"/>
-    <mergeCell ref="E31:H31"/>
-    <mergeCell ref="E30:H30"/>
-    <mergeCell ref="E32:H32"/>
-    <mergeCell ref="E33:H33"/>
-    <mergeCell ref="E35:H35"/>
     <mergeCell ref="B59:J61"/>
     <mergeCell ref="E41:H41"/>
     <mergeCell ref="E52:H52"/>
@@ -58710,6 +58678,37 @@
     <mergeCell ref="E47:H47"/>
     <mergeCell ref="E48:H48"/>
     <mergeCell ref="E49:H49"/>
+    <mergeCell ref="D21:E21"/>
+    <mergeCell ref="I21:J21"/>
+    <mergeCell ref="E25:H25"/>
+    <mergeCell ref="E26:H26"/>
+    <mergeCell ref="B58:K58"/>
+    <mergeCell ref="E50:H50"/>
+    <mergeCell ref="E51:H51"/>
+    <mergeCell ref="E27:H27"/>
+    <mergeCell ref="E28:H28"/>
+    <mergeCell ref="E29:H29"/>
+    <mergeCell ref="E31:H31"/>
+    <mergeCell ref="E30:H30"/>
+    <mergeCell ref="E32:H32"/>
+    <mergeCell ref="E33:H33"/>
+    <mergeCell ref="E35:H35"/>
+    <mergeCell ref="D12:E12"/>
+    <mergeCell ref="D13:E13"/>
+    <mergeCell ref="D14:E14"/>
+    <mergeCell ref="H15:J15"/>
+    <mergeCell ref="D18:J18"/>
+    <mergeCell ref="C7:D7"/>
+    <mergeCell ref="G7:H7"/>
+    <mergeCell ref="I7:J7"/>
+    <mergeCell ref="D9:F9"/>
+    <mergeCell ref="H9:J9"/>
+    <mergeCell ref="E40:H40"/>
+    <mergeCell ref="E34:H34"/>
+    <mergeCell ref="E36:H36"/>
+    <mergeCell ref="E37:H37"/>
+    <mergeCell ref="E38:H38"/>
+    <mergeCell ref="E39:H39"/>
   </mergeCells>
   <phoneticPr fontId="30" type="noConversion"/>
   <printOptions horizontalCentered="1" verticalCentered="1" gridLines="1"/>
@@ -58881,8 +58880,8 @@
     <row r="7" spans="1:26" ht="21" customHeight="1">
       <c r="A7" s="1"/>
       <c r="B7" s="1"/>
-      <c r="C7" s="159"/>
-      <c r="D7" s="109"/>
+      <c r="C7" s="161"/>
+      <c r="D7" s="137"/>
       <c r="E7" s="11" t="s">
         <v>1</v>
       </c>
@@ -58891,8 +58890,8 @@
       <c r="H7" s="6"/>
       <c r="I7" s="6"/>
       <c r="J7" s="1"/>
-      <c r="K7" s="147"/>
-      <c r="L7" s="111"/>
+      <c r="K7" s="160"/>
+      <c r="L7" s="113"/>
       <c r="M7" s="1"/>
       <c r="N7" s="1"/>
       <c r="O7" s="1"/>
@@ -58937,19 +58936,19 @@
       <c r="F9" s="13" t="s">
         <v>4</v>
       </c>
-      <c r="G9" s="160" t="s">
+      <c r="G9" s="162" t="s">
         <v>5</v>
       </c>
-      <c r="H9" s="111"/>
-      <c r="I9" s="111"/>
+      <c r="H9" s="113"/>
+      <c r="I9" s="113"/>
       <c r="J9" s="1"/>
       <c r="K9" s="1"/>
       <c r="L9" s="1"/>
       <c r="M9" s="1"/>
       <c r="N9" s="1"/>
-      <c r="O9" s="147"/>
-      <c r="P9" s="111"/>
-      <c r="Q9" s="111"/>
+      <c r="O9" s="160"/>
+      <c r="P9" s="113"/>
+      <c r="Q9" s="113"/>
       <c r="R9" s="1"/>
       <c r="S9" s="1"/>
       <c r="T9" s="1"/>
@@ -58963,10 +58962,10 @@
     <row r="10" spans="1:26" ht="28.5" customHeight="1">
       <c r="A10" s="1"/>
       <c r="B10" s="1"/>
-      <c r="C10" s="161" t="s">
+      <c r="C10" s="163" t="s">
         <v>7</v>
       </c>
-      <c r="D10" s="164"/>
+      <c r="D10" s="166"/>
       <c r="E10" s="1"/>
       <c r="F10" s="21" t="s">
         <v>9</v>
@@ -58981,8 +58980,8 @@
         <v>12</v>
       </c>
       <c r="J10" s="1"/>
-      <c r="K10" s="163"/>
-      <c r="L10" s="163"/>
+      <c r="K10" s="165"/>
+      <c r="L10" s="165"/>
       <c r="M10" s="1"/>
       <c r="N10" s="1"/>
       <c r="O10" s="1"/>
@@ -59001,8 +59000,8 @@
     <row r="11" spans="1:26" ht="19.5" customHeight="1">
       <c r="A11" s="1"/>
       <c r="B11" s="1"/>
-      <c r="C11" s="162"/>
-      <c r="D11" s="162"/>
+      <c r="C11" s="164"/>
+      <c r="D11" s="164"/>
       <c r="E11" s="1"/>
       <c r="F11" s="21" t="s">
         <v>17</v>
@@ -59017,8 +59016,8 @@
         <v>20</v>
       </c>
       <c r="J11" s="1"/>
-      <c r="K11" s="162"/>
-      <c r="L11" s="162"/>
+      <c r="K11" s="164"/>
+      <c r="L11" s="164"/>
       <c r="M11" s="1"/>
       <c r="N11" s="1"/>
       <c r="O11" s="1"/>
@@ -59190,31 +59189,31 @@
       <c r="C17" s="39" t="s">
         <v>29</v>
       </c>
-      <c r="D17" s="165" t="s">
+      <c r="D17" s="167" t="s">
         <v>30</v>
       </c>
-      <c r="E17" s="111"/>
+      <c r="E17" s="113"/>
       <c r="F17" s="40" t="s">
         <v>31</v>
       </c>
       <c r="G17" s="39" t="s">
         <v>33</v>
       </c>
-      <c r="H17" s="166">
+      <c r="H17" s="168">
         <f>G54</f>
         <v>0</v>
       </c>
-      <c r="I17" s="111"/>
+      <c r="I17" s="113"/>
       <c r="J17" s="45" t="s">
         <v>37</v>
       </c>
       <c r="K17" s="1"/>
-      <c r="L17" s="147"/>
-      <c r="M17" s="111"/>
+      <c r="L17" s="160"/>
+      <c r="M17" s="113"/>
       <c r="N17" s="1"/>
       <c r="O17" s="1"/>
-      <c r="P17" s="147"/>
-      <c r="Q17" s="111"/>
+      <c r="P17" s="160"/>
+      <c r="Q17" s="113"/>
       <c r="R17" s="1"/>
       <c r="S17" s="1"/>
       <c r="T17" s="1"/>
@@ -59346,10 +59345,10 @@
       <c r="D22" s="52" t="s">
         <v>59</v>
       </c>
-      <c r="E22" s="157" t="s">
+      <c r="E22" s="173" t="s">
         <v>40</v>
       </c>
-      <c r="F22" s="158"/>
+      <c r="F22" s="174"/>
       <c r="G22" s="52" t="s">
         <v>41</v>
       </c>
@@ -59362,8 +59361,8 @@
       <c r="J22" s="12"/>
       <c r="K22" s="1"/>
       <c r="L22" s="1"/>
-      <c r="M22" s="147"/>
-      <c r="N22" s="111"/>
+      <c r="M22" s="160"/>
+      <c r="N22" s="113"/>
       <c r="O22" s="1"/>
       <c r="P22" s="1"/>
       <c r="Q22" s="1"/>
@@ -59385,15 +59384,15 @@
       </c>
       <c r="D23" s="59"/>
       <c r="E23" s="155"/>
-      <c r="F23" s="152"/>
+      <c r="F23" s="156"/>
       <c r="G23" s="63"/>
       <c r="H23" s="65"/>
       <c r="I23" s="66"/>
       <c r="J23" s="12"/>
       <c r="K23" s="1"/>
       <c r="L23" s="1"/>
-      <c r="M23" s="147"/>
-      <c r="N23" s="111"/>
+      <c r="M23" s="160"/>
+      <c r="N23" s="113"/>
       <c r="O23" s="1"/>
       <c r="P23" s="1"/>
       <c r="Q23" s="1"/>
@@ -59414,8 +59413,8 @@
         <v>2</v>
       </c>
       <c r="D24" s="68"/>
-      <c r="E24" s="100"/>
-      <c r="F24" s="102"/>
+      <c r="E24" s="155"/>
+      <c r="F24" s="156"/>
       <c r="G24" s="65"/>
       <c r="H24" s="65"/>
       <c r="I24" s="100"/>
@@ -59423,7 +59422,7 @@
       <c r="K24" s="97"/>
       <c r="L24" s="97"/>
       <c r="M24" s="97"/>
-      <c r="N24" s="103"/>
+      <c r="N24" s="102"/>
       <c r="O24" s="97"/>
       <c r="P24" s="97"/>
       <c r="Q24" s="97"/>
@@ -59444,8 +59443,8 @@
         <v>3</v>
       </c>
       <c r="D25" s="68"/>
-      <c r="E25" s="100"/>
-      <c r="F25" s="102"/>
+      <c r="E25" s="155"/>
+      <c r="F25" s="156"/>
       <c r="G25" s="65"/>
       <c r="H25" s="65"/>
       <c r="I25" s="100"/>
@@ -59453,7 +59452,7 @@
       <c r="K25" s="97"/>
       <c r="L25" s="97"/>
       <c r="M25" s="97"/>
-      <c r="N25" s="103"/>
+      <c r="N25" s="102"/>
       <c r="O25" s="97"/>
       <c r="P25" s="97"/>
       <c r="Q25" s="97"/>
@@ -59474,8 +59473,8 @@
         <v>4</v>
       </c>
       <c r="D26" s="68"/>
-      <c r="E26" s="100"/>
-      <c r="F26" s="102"/>
+      <c r="E26" s="155"/>
+      <c r="F26" s="156"/>
       <c r="G26" s="65"/>
       <c r="H26" s="65"/>
       <c r="I26" s="100"/>
@@ -59483,7 +59482,7 @@
       <c r="K26" s="97"/>
       <c r="L26" s="97"/>
       <c r="M26" s="97"/>
-      <c r="N26" s="103"/>
+      <c r="N26" s="102"/>
       <c r="O26" s="97"/>
       <c r="P26" s="97"/>
       <c r="Q26" s="97"/>
@@ -59504,8 +59503,8 @@
         <v>5</v>
       </c>
       <c r="D27" s="68"/>
-      <c r="E27" s="100"/>
-      <c r="F27" s="102"/>
+      <c r="E27" s="155"/>
+      <c r="F27" s="156"/>
       <c r="G27" s="65"/>
       <c r="H27" s="65"/>
       <c r="I27" s="100"/>
@@ -59513,7 +59512,7 @@
       <c r="K27" s="97"/>
       <c r="L27" s="97"/>
       <c r="M27" s="97"/>
-      <c r="N27" s="103"/>
+      <c r="N27" s="102"/>
       <c r="O27" s="97"/>
       <c r="P27" s="97"/>
       <c r="Q27" s="97"/>
@@ -59534,8 +59533,8 @@
         <v>6</v>
       </c>
       <c r="D28" s="68"/>
-      <c r="E28" s="100"/>
-      <c r="F28" s="102"/>
+      <c r="E28" s="155"/>
+      <c r="F28" s="156"/>
       <c r="G28" s="65"/>
       <c r="H28" s="65"/>
       <c r="I28" s="100"/>
@@ -59543,7 +59542,7 @@
       <c r="K28" s="97"/>
       <c r="L28" s="97"/>
       <c r="M28" s="97"/>
-      <c r="N28" s="103"/>
+      <c r="N28" s="102"/>
       <c r="O28" s="97"/>
       <c r="P28" s="97"/>
       <c r="Q28" s="97"/>
@@ -59564,8 +59563,8 @@
         <v>7</v>
       </c>
       <c r="D29" s="68"/>
-      <c r="E29" s="100"/>
-      <c r="F29" s="102"/>
+      <c r="E29" s="155"/>
+      <c r="F29" s="156"/>
       <c r="G29" s="65"/>
       <c r="H29" s="65"/>
       <c r="I29" s="100"/>
@@ -59573,7 +59572,7 @@
       <c r="K29" s="97"/>
       <c r="L29" s="97"/>
       <c r="M29" s="97"/>
-      <c r="N29" s="103"/>
+      <c r="N29" s="102"/>
       <c r="O29" s="97"/>
       <c r="P29" s="97"/>
       <c r="Q29" s="97"/>
@@ -59594,8 +59593,8 @@
         <v>8</v>
       </c>
       <c r="D30" s="68"/>
-      <c r="E30" s="100"/>
-      <c r="F30" s="102"/>
+      <c r="E30" s="155"/>
+      <c r="F30" s="156"/>
       <c r="G30" s="65"/>
       <c r="H30" s="65"/>
       <c r="I30" s="100"/>
@@ -59603,7 +59602,7 @@
       <c r="K30" s="97"/>
       <c r="L30" s="97"/>
       <c r="M30" s="97"/>
-      <c r="N30" s="103"/>
+      <c r="N30" s="102"/>
       <c r="O30" s="97"/>
       <c r="P30" s="97"/>
       <c r="Q30" s="97"/>
@@ -59624,8 +59623,8 @@
         <v>9</v>
       </c>
       <c r="D31" s="68"/>
-      <c r="E31" s="100"/>
-      <c r="F31" s="102"/>
+      <c r="E31" s="155"/>
+      <c r="F31" s="156"/>
       <c r="G31" s="65"/>
       <c r="H31" s="65"/>
       <c r="I31" s="100"/>
@@ -59633,7 +59632,7 @@
       <c r="K31" s="97"/>
       <c r="L31" s="97"/>
       <c r="M31" s="97"/>
-      <c r="N31" s="103"/>
+      <c r="N31" s="102"/>
       <c r="O31" s="97"/>
       <c r="P31" s="97"/>
       <c r="Q31" s="97"/>
@@ -59654,8 +59653,8 @@
         <v>10</v>
       </c>
       <c r="D32" s="68"/>
-      <c r="E32" s="100"/>
-      <c r="F32" s="102"/>
+      <c r="E32" s="155"/>
+      <c r="F32" s="156"/>
       <c r="G32" s="65"/>
       <c r="H32" s="65"/>
       <c r="I32" s="100"/>
@@ -59663,7 +59662,7 @@
       <c r="K32" s="97"/>
       <c r="L32" s="97"/>
       <c r="M32" s="97"/>
-      <c r="N32" s="103"/>
+      <c r="N32" s="102"/>
       <c r="O32" s="97"/>
       <c r="P32" s="97"/>
       <c r="Q32" s="97"/>
@@ -59684,8 +59683,8 @@
         <v>11</v>
       </c>
       <c r="D33" s="68"/>
-      <c r="E33" s="100"/>
-      <c r="F33" s="102"/>
+      <c r="E33" s="155"/>
+      <c r="F33" s="156"/>
       <c r="G33" s="65"/>
       <c r="H33" s="65"/>
       <c r="I33" s="100"/>
@@ -59693,7 +59692,7 @@
       <c r="K33" s="97"/>
       <c r="L33" s="97"/>
       <c r="M33" s="97"/>
-      <c r="N33" s="103"/>
+      <c r="N33" s="102"/>
       <c r="O33" s="97"/>
       <c r="P33" s="97"/>
       <c r="Q33" s="97"/>
@@ -59714,8 +59713,8 @@
         <v>12</v>
       </c>
       <c r="D34" s="68"/>
-      <c r="E34" s="100"/>
-      <c r="F34" s="102"/>
+      <c r="E34" s="155"/>
+      <c r="F34" s="156"/>
       <c r="G34" s="65"/>
       <c r="H34" s="65"/>
       <c r="I34" s="100"/>
@@ -59723,7 +59722,7 @@
       <c r="K34" s="97"/>
       <c r="L34" s="97"/>
       <c r="M34" s="97"/>
-      <c r="N34" s="103"/>
+      <c r="N34" s="102"/>
       <c r="O34" s="97"/>
       <c r="P34" s="97"/>
       <c r="Q34" s="97"/>
@@ -59744,8 +59743,8 @@
         <v>13</v>
       </c>
       <c r="D35" s="68"/>
-      <c r="E35" s="100"/>
-      <c r="F35" s="102"/>
+      <c r="E35" s="155"/>
+      <c r="F35" s="156"/>
       <c r="G35" s="65"/>
       <c r="H35" s="65"/>
       <c r="I35" s="100"/>
@@ -59753,7 +59752,7 @@
       <c r="K35" s="97"/>
       <c r="L35" s="97"/>
       <c r="M35" s="97"/>
-      <c r="N35" s="103"/>
+      <c r="N35" s="102"/>
       <c r="O35" s="97"/>
       <c r="P35" s="97"/>
       <c r="Q35" s="97"/>
@@ -59774,8 +59773,8 @@
         <v>14</v>
       </c>
       <c r="D36" s="68"/>
-      <c r="E36" s="100"/>
-      <c r="F36" s="102"/>
+      <c r="E36" s="155"/>
+      <c r="F36" s="156"/>
       <c r="G36" s="65"/>
       <c r="H36" s="65"/>
       <c r="I36" s="100"/>
@@ -59783,7 +59782,7 @@
       <c r="K36" s="97"/>
       <c r="L36" s="97"/>
       <c r="M36" s="97"/>
-      <c r="N36" s="103"/>
+      <c r="N36" s="102"/>
       <c r="O36" s="97"/>
       <c r="P36" s="97"/>
       <c r="Q36" s="97"/>
@@ -59804,8 +59803,8 @@
         <v>15</v>
       </c>
       <c r="D37" s="68"/>
-      <c r="E37" s="100"/>
-      <c r="F37" s="102"/>
+      <c r="E37" s="155"/>
+      <c r="F37" s="156"/>
       <c r="G37" s="65"/>
       <c r="H37" s="65"/>
       <c r="I37" s="100"/>
@@ -59813,7 +59812,7 @@
       <c r="K37" s="97"/>
       <c r="L37" s="97"/>
       <c r="M37" s="97"/>
-      <c r="N37" s="103"/>
+      <c r="N37" s="102"/>
       <c r="O37" s="97"/>
       <c r="P37" s="97"/>
       <c r="Q37" s="97"/>
@@ -59835,15 +59834,15 @@
       </c>
       <c r="D38" s="68"/>
       <c r="E38" s="155"/>
-      <c r="F38" s="152"/>
+      <c r="F38" s="156"/>
       <c r="G38" s="65"/>
       <c r="H38" s="65"/>
       <c r="I38" s="66"/>
       <c r="J38" s="12"/>
       <c r="K38" s="1"/>
       <c r="L38" s="1"/>
-      <c r="M38" s="147"/>
-      <c r="N38" s="111"/>
+      <c r="M38" s="160"/>
+      <c r="N38" s="113"/>
       <c r="O38" s="1"/>
       <c r="P38" s="1"/>
       <c r="Q38" s="1"/>
@@ -60083,7 +60082,7 @@
       <c r="K46" s="97"/>
       <c r="L46" s="97"/>
       <c r="M46" s="97"/>
-      <c r="N46" s="103"/>
+      <c r="N46" s="102"/>
       <c r="O46" s="97"/>
       <c r="P46" s="97"/>
       <c r="Q46" s="97"/>
@@ -60113,7 +60112,7 @@
       <c r="K47" s="97"/>
       <c r="L47" s="97"/>
       <c r="M47" s="97"/>
-      <c r="N47" s="103"/>
+      <c r="N47" s="102"/>
       <c r="O47" s="97"/>
       <c r="P47" s="97"/>
       <c r="Q47" s="97"/>
@@ -60143,7 +60142,7 @@
       <c r="K48" s="97"/>
       <c r="L48" s="97"/>
       <c r="M48" s="97"/>
-      <c r="N48" s="103"/>
+      <c r="N48" s="102"/>
       <c r="O48" s="97"/>
       <c r="P48" s="97"/>
       <c r="Q48" s="97"/>
@@ -60172,8 +60171,8 @@
       <c r="J49" s="12"/>
       <c r="K49" s="1"/>
       <c r="L49" s="1"/>
-      <c r="M49" s="147"/>
-      <c r="N49" s="111"/>
+      <c r="M49" s="160"/>
+      <c r="N49" s="113"/>
       <c r="O49" s="1"/>
       <c r="P49" s="1"/>
       <c r="Q49" s="1"/>
@@ -60195,15 +60194,15 @@
       </c>
       <c r="D50" s="68"/>
       <c r="E50" s="155"/>
-      <c r="F50" s="152"/>
+      <c r="F50" s="157"/>
       <c r="G50" s="65"/>
       <c r="H50" s="65"/>
       <c r="I50" s="66"/>
       <c r="J50" s="12"/>
       <c r="K50" s="1"/>
       <c r="L50" s="1"/>
-      <c r="M50" s="147"/>
-      <c r="N50" s="111"/>
+      <c r="M50" s="160"/>
+      <c r="N50" s="113"/>
       <c r="O50" s="1"/>
       <c r="P50" s="1"/>
       <c r="Q50" s="1"/>
@@ -60225,15 +60224,15 @@
       </c>
       <c r="D51" s="68"/>
       <c r="E51" s="155"/>
-      <c r="F51" s="152"/>
+      <c r="F51" s="157"/>
       <c r="G51" s="65"/>
       <c r="H51" s="65"/>
       <c r="I51" s="66"/>
       <c r="J51" s="12"/>
       <c r="K51" s="1"/>
       <c r="L51" s="1"/>
-      <c r="M51" s="147"/>
-      <c r="N51" s="111"/>
+      <c r="M51" s="160"/>
+      <c r="N51" s="113"/>
       <c r="O51" s="1"/>
       <c r="P51" s="1"/>
       <c r="Q51" s="1"/>
@@ -60250,26 +60249,26 @@
     <row r="52" spans="1:26" ht="27.75" customHeight="1">
       <c r="A52" s="1"/>
       <c r="B52" s="12"/>
-      <c r="C52" s="150" t="s">
+      <c r="C52" s="169" t="s">
         <v>41</v>
       </c>
-      <c r="D52" s="151"/>
-      <c r="E52" s="151"/>
-      <c r="F52" s="152"/>
-      <c r="G52" s="153">
+      <c r="D52" s="170"/>
+      <c r="E52" s="170"/>
+      <c r="F52" s="157"/>
+      <c r="G52" s="171">
         <f>SUM(G23:G51)</f>
         <v>0</v>
       </c>
-      <c r="H52" s="151"/>
-      <c r="I52" s="152"/>
+      <c r="H52" s="170"/>
+      <c r="I52" s="157"/>
       <c r="J52" s="12"/>
-      <c r="K52" s="147"/>
-      <c r="L52" s="111"/>
-      <c r="M52" s="111"/>
-      <c r="N52" s="111"/>
-      <c r="O52" s="177"/>
-      <c r="P52" s="149"/>
-      <c r="Q52" s="149"/>
+      <c r="K52" s="160"/>
+      <c r="L52" s="113"/>
+      <c r="M52" s="113"/>
+      <c r="N52" s="113"/>
+      <c r="O52" s="158"/>
+      <c r="P52" s="159"/>
+      <c r="Q52" s="159"/>
       <c r="R52" s="1"/>
       <c r="S52" s="1"/>
       <c r="T52" s="1"/>
@@ -60283,26 +60282,26 @@
     <row r="53" spans="1:26" ht="27.75" customHeight="1">
       <c r="A53" s="1"/>
       <c r="B53" s="12"/>
-      <c r="C53" s="150" t="s">
+      <c r="C53" s="169" t="s">
         <v>52</v>
       </c>
-      <c r="D53" s="151"/>
-      <c r="E53" s="151"/>
-      <c r="F53" s="152"/>
-      <c r="G53" s="153">
+      <c r="D53" s="170"/>
+      <c r="E53" s="170"/>
+      <c r="F53" s="157"/>
+      <c r="G53" s="171">
         <f>SUM(H23:H51)</f>
         <v>0</v>
       </c>
-      <c r="H53" s="151"/>
-      <c r="I53" s="152"/>
+      <c r="H53" s="170"/>
+      <c r="I53" s="157"/>
       <c r="J53" s="12"/>
-      <c r="K53" s="147"/>
-      <c r="L53" s="111"/>
-      <c r="M53" s="111"/>
-      <c r="N53" s="111"/>
-      <c r="O53" s="147"/>
-      <c r="P53" s="111"/>
-      <c r="Q53" s="111"/>
+      <c r="K53" s="160"/>
+      <c r="L53" s="113"/>
+      <c r="M53" s="113"/>
+      <c r="N53" s="113"/>
+      <c r="O53" s="160"/>
+      <c r="P53" s="113"/>
+      <c r="Q53" s="113"/>
       <c r="R53" s="1"/>
       <c r="S53" s="1"/>
       <c r="T53" s="1"/>
@@ -60316,26 +60315,26 @@
     <row r="54" spans="1:26" ht="27.75" customHeight="1">
       <c r="A54" s="1"/>
       <c r="B54" s="12"/>
-      <c r="C54" s="150" t="s">
+      <c r="C54" s="169" t="s">
         <v>55</v>
       </c>
-      <c r="D54" s="151"/>
-      <c r="E54" s="151"/>
-      <c r="F54" s="152"/>
-      <c r="G54" s="154">
+      <c r="D54" s="170"/>
+      <c r="E54" s="170"/>
+      <c r="F54" s="157"/>
+      <c r="G54" s="172">
         <f>SUM(G52:I53)</f>
         <v>0</v>
       </c>
-      <c r="H54" s="151"/>
-      <c r="I54" s="151"/>
+      <c r="H54" s="170"/>
+      <c r="I54" s="170"/>
       <c r="J54" s="12"/>
-      <c r="K54" s="147"/>
-      <c r="L54" s="111"/>
-      <c r="M54" s="111"/>
-      <c r="N54" s="111"/>
-      <c r="O54" s="147"/>
-      <c r="P54" s="111"/>
-      <c r="Q54" s="111"/>
+      <c r="K54" s="160"/>
+      <c r="L54" s="113"/>
+      <c r="M54" s="113"/>
+      <c r="N54" s="113"/>
+      <c r="O54" s="160"/>
+      <c r="P54" s="113"/>
+      <c r="Q54" s="113"/>
       <c r="R54" s="1"/>
       <c r="S54" s="1"/>
       <c r="T54" s="1"/>
@@ -60349,23 +60348,23 @@
     <row r="55" spans="1:26" ht="27.75" customHeight="1">
       <c r="A55" s="1"/>
       <c r="B55" s="1"/>
-      <c r="C55" s="146" t="s">
+      <c r="C55" s="175" t="s">
         <v>57</v>
       </c>
-      <c r="D55" s="109"/>
-      <c r="E55" s="109"/>
-      <c r="F55" s="109"/>
-      <c r="G55" s="109"/>
-      <c r="H55" s="109"/>
-      <c r="I55" s="109"/>
+      <c r="D55" s="137"/>
+      <c r="E55" s="137"/>
+      <c r="F55" s="137"/>
+      <c r="G55" s="137"/>
+      <c r="H55" s="137"/>
+      <c r="I55" s="137"/>
       <c r="J55" s="1"/>
-      <c r="K55" s="148"/>
-      <c r="L55" s="149"/>
-      <c r="M55" s="149"/>
-      <c r="N55" s="149"/>
-      <c r="O55" s="149"/>
-      <c r="P55" s="149"/>
-      <c r="Q55" s="149"/>
+      <c r="K55" s="176"/>
+      <c r="L55" s="159"/>
+      <c r="M55" s="159"/>
+      <c r="N55" s="159"/>
+      <c r="O55" s="159"/>
+      <c r="P55" s="159"/>
+      <c r="Q55" s="159"/>
       <c r="R55" s="1"/>
       <c r="S55" s="1"/>
       <c r="T55" s="1"/>
@@ -60379,21 +60378,21 @@
     <row r="56" spans="1:26" ht="27.75" customHeight="1">
       <c r="A56" s="1"/>
       <c r="B56" s="1"/>
-      <c r="C56" s="108"/>
-      <c r="D56" s="109"/>
-      <c r="E56" s="109"/>
-      <c r="F56" s="109"/>
-      <c r="G56" s="109"/>
-      <c r="H56" s="109"/>
-      <c r="I56" s="109"/>
+      <c r="C56" s="136"/>
+      <c r="D56" s="137"/>
+      <c r="E56" s="137"/>
+      <c r="F56" s="137"/>
+      <c r="G56" s="137"/>
+      <c r="H56" s="137"/>
+      <c r="I56" s="137"/>
       <c r="J56" s="1"/>
-      <c r="K56" s="108"/>
-      <c r="L56" s="109"/>
-      <c r="M56" s="109"/>
-      <c r="N56" s="109"/>
-      <c r="O56" s="109"/>
-      <c r="P56" s="109"/>
-      <c r="Q56" s="109"/>
+      <c r="K56" s="136"/>
+      <c r="L56" s="137"/>
+      <c r="M56" s="137"/>
+      <c r="N56" s="137"/>
+      <c r="O56" s="137"/>
+      <c r="P56" s="137"/>
+      <c r="Q56" s="137"/>
       <c r="R56" s="1"/>
       <c r="S56" s="1"/>
       <c r="T56" s="1"/>
@@ -60407,21 +60406,21 @@
     <row r="57" spans="1:26" ht="27.75" customHeight="1">
       <c r="A57" s="1"/>
       <c r="B57" s="1"/>
-      <c r="C57" s="108"/>
-      <c r="D57" s="109"/>
-      <c r="E57" s="109"/>
-      <c r="F57" s="109"/>
-      <c r="G57" s="109"/>
-      <c r="H57" s="109"/>
-      <c r="I57" s="109"/>
+      <c r="C57" s="136"/>
+      <c r="D57" s="137"/>
+      <c r="E57" s="137"/>
+      <c r="F57" s="137"/>
+      <c r="G57" s="137"/>
+      <c r="H57" s="137"/>
+      <c r="I57" s="137"/>
       <c r="J57" s="1"/>
-      <c r="K57" s="108"/>
-      <c r="L57" s="109"/>
-      <c r="M57" s="109"/>
-      <c r="N57" s="109"/>
-      <c r="O57" s="109"/>
-      <c r="P57" s="109"/>
-      <c r="Q57" s="109"/>
+      <c r="K57" s="136"/>
+      <c r="L57" s="137"/>
+      <c r="M57" s="137"/>
+      <c r="N57" s="137"/>
+      <c r="O57" s="137"/>
+      <c r="P57" s="137"/>
+      <c r="Q57" s="137"/>
       <c r="R57" s="1"/>
       <c r="S57" s="1"/>
       <c r="T57" s="1"/>
@@ -66124,17 +66123,32 @@
       <c r="Z262" s="1"/>
     </row>
   </sheetData>
-  <mergeCells count="48">
-    <mergeCell ref="E44:F44"/>
-    <mergeCell ref="E45:F45"/>
-    <mergeCell ref="E46:F46"/>
-    <mergeCell ref="E47:F47"/>
-    <mergeCell ref="E48:F48"/>
-    <mergeCell ref="E23:F23"/>
-    <mergeCell ref="E40:F40"/>
-    <mergeCell ref="E41:F41"/>
-    <mergeCell ref="E42:F42"/>
-    <mergeCell ref="E43:F43"/>
+  <mergeCells count="62">
+    <mergeCell ref="E35:F35"/>
+    <mergeCell ref="E36:F36"/>
+    <mergeCell ref="E37:F37"/>
+    <mergeCell ref="C55:I57"/>
+    <mergeCell ref="K53:N53"/>
+    <mergeCell ref="O53:Q53"/>
+    <mergeCell ref="K54:N54"/>
+    <mergeCell ref="O54:Q54"/>
+    <mergeCell ref="K55:Q57"/>
+    <mergeCell ref="M22:N22"/>
+    <mergeCell ref="C53:F53"/>
+    <mergeCell ref="G53:I53"/>
+    <mergeCell ref="C54:F54"/>
+    <mergeCell ref="G54:I54"/>
+    <mergeCell ref="E38:F38"/>
+    <mergeCell ref="M38:N38"/>
+    <mergeCell ref="E49:F49"/>
+    <mergeCell ref="M49:N49"/>
+    <mergeCell ref="E50:F50"/>
+    <mergeCell ref="M50:N50"/>
+    <mergeCell ref="E51:F51"/>
+    <mergeCell ref="C52:F52"/>
+    <mergeCell ref="G52:I52"/>
+    <mergeCell ref="K52:N52"/>
+    <mergeCell ref="E22:F22"/>
     <mergeCell ref="O52:Q52"/>
     <mergeCell ref="M51:N51"/>
     <mergeCell ref="E39:F39"/>
@@ -66151,28 +66165,27 @@
     <mergeCell ref="H17:I17"/>
     <mergeCell ref="L17:M17"/>
     <mergeCell ref="P17:Q17"/>
-    <mergeCell ref="M22:N22"/>
-    <mergeCell ref="C53:F53"/>
-    <mergeCell ref="G53:I53"/>
-    <mergeCell ref="C54:F54"/>
-    <mergeCell ref="G54:I54"/>
-    <mergeCell ref="E38:F38"/>
-    <mergeCell ref="M38:N38"/>
-    <mergeCell ref="E49:F49"/>
-    <mergeCell ref="M49:N49"/>
-    <mergeCell ref="E50:F50"/>
-    <mergeCell ref="M50:N50"/>
-    <mergeCell ref="E51:F51"/>
-    <mergeCell ref="C52:F52"/>
-    <mergeCell ref="G52:I52"/>
-    <mergeCell ref="K52:N52"/>
-    <mergeCell ref="E22:F22"/>
-    <mergeCell ref="C55:I57"/>
-    <mergeCell ref="K53:N53"/>
-    <mergeCell ref="O53:Q53"/>
-    <mergeCell ref="K54:N54"/>
-    <mergeCell ref="O54:Q54"/>
-    <mergeCell ref="K55:Q57"/>
+    <mergeCell ref="E23:F23"/>
+    <mergeCell ref="E40:F40"/>
+    <mergeCell ref="E41:F41"/>
+    <mergeCell ref="E42:F42"/>
+    <mergeCell ref="E43:F43"/>
+    <mergeCell ref="E24:F24"/>
+    <mergeCell ref="E25:F25"/>
+    <mergeCell ref="E26:F26"/>
+    <mergeCell ref="E27:F27"/>
+    <mergeCell ref="E28:F28"/>
+    <mergeCell ref="E29:F29"/>
+    <mergeCell ref="E30:F30"/>
+    <mergeCell ref="E31:F31"/>
+    <mergeCell ref="E32:F32"/>
+    <mergeCell ref="E33:F33"/>
+    <mergeCell ref="E34:F34"/>
+    <mergeCell ref="E44:F44"/>
+    <mergeCell ref="E45:F45"/>
+    <mergeCell ref="E46:F46"/>
+    <mergeCell ref="E47:F47"/>
+    <mergeCell ref="E48:F48"/>
   </mergeCells>
   <phoneticPr fontId="30" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0" footer="0"/>
